--- a/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
+++ b/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
@@ -206,39 +206,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Test Case No.</t>
+          <t>用例编号</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>测试模块</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>模块</t>
+          <t>用例名称</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>前置条件</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>测试点</t>
+          <t>测试步骤</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -248,12 +247,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>需求疑问/风险</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>测试结果</t>
+          <t>第一轮实际结果</t>
         </is>
       </c>
     </row>
@@ -265,22 +259,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户入口 - 个人用户进入美国账户开户申请页</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>开户入口</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>个人用户进入美国账户开户申请页</t>
+          <t>在 Fidère 客户端验证：个人用户进入美国账户开户申请页</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -289,11 +283,6 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -307,35 +296,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户入口 - 企业用户尝试进入个人美国账户开户流程</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>开户入口</t>
+          <t>存在企业用户或非个人用户账号。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>企业用户尝试进入个人美国账户开户流程</t>
+          <t>在 Fidère 客户端验证：企业用户尝试进入个人美国账户开户流程</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>系统不允许进入个人美国账户开户流程，或展示不适用提示</t>
+          <t>系统不允许进入个人美国账户开户流程，或展示不适用提示；当前原型存在企业开户切换入口，企业限制为原型待补充</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>当前原型存在企业开户切换入口，企业限制为原型待补充</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -349,22 +333,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户资料填写 - 开户申请页展示开户资料区域</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>开户资料填写</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>开户申请页展示开户资料区域</t>
+          <t>在 Fidère 客户端验证：开户申请页展示开户资料区域</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -373,11 +357,6 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -391,22 +370,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户资料填写 - 开户必填字段为空时提交申请</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>开户资料填写</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>开户必填字段为空时提交申请</t>
+          <t>在 Fidère 客户端验证：开户必填字段为空时提交申请</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -415,11 +394,6 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -433,22 +407,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户资料填写 - 填写合法开户关键字段后继续下一步</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>开户资料填写</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>填写合法开户关键字段后继续下一步</t>
+          <t>在 Fidère 客户端验证：填写合法开户关键字段后继续下一步</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -457,11 +431,6 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -475,22 +444,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户资料填写 - 国家/地区、证件类型、出生日期等选择类字段正常选择</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>开户资料填写</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国家/地区、证件类型、出生日期等选择类字段正常选择</t>
+          <t>在 Fidère 客户端验证：国家/地区、证件类型、出生日期等选择类字段正常选择</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -499,11 +468,6 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -517,22 +481,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户提交 - 资料和文件完整后提交美国账户开户申请</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>开户提交</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>资料和文件完整后提交美国账户开户申请</t>
+          <t>在 Fidère 客户端验证：资料和文件完整后提交美国账户开户申请</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -541,11 +505,6 @@
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -559,22 +518,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>开户状态 - 开户申请提交成功后查看客户端状态</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>开户状态</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>开户申请提交成功后查看客户端状态</t>
+          <t>在 Fidère 客户端验证：开户申请提交成功后查看客户端状态</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -583,11 +542,6 @@
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -601,22 +555,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件上传 - 上传护照文件</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>上传护照文件</t>
+          <t>在 Fidère 客户端验证：上传护照文件</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -625,11 +579,6 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -643,22 +592,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件上传 - 上传身份证明文件</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>上传身份证明文件</t>
+          <t>在 Fidère 客户端验证：上传身份证明文件</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -667,11 +616,6 @@
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -685,22 +629,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件上传 - 上传自拍照文件</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>上传自拍照文件</t>
+          <t>在 Fidère 客户端验证：上传自拍照文件</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -709,11 +653,6 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -727,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件上传 - 上传地址证明文件</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>上传地址证明文件</t>
+          <t>在 Fidère 客户端验证：上传地址证明文件</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -751,11 +690,6 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -769,22 +703,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件上传 - 上传资金来源证明文件</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>上传资金来源证明文件</t>
+          <t>在 Fidère 客户端验证：上传资金来源证明文件</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -793,11 +727,6 @@
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -811,22 +740,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件上传 - 缺少必填证明文件时提交开户申请</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>缺少必填证明文件时提交开户申请</t>
+          <t>在 Fidère 客户端验证：缺少必填证明文件时提交开户申请</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -835,11 +764,6 @@
         </is>
       </c>
       <c r="G15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -853,22 +777,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件替换 - 普通证明文件替换为新文件</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>文件替换</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>普通证明文件替换为新文件</t>
+          <t>在 Fidère 客户端验证：普通证明文件替换为新文件</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -877,11 +801,6 @@
         </is>
       </c>
       <c r="G16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -895,35 +814,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>文件替换 - 替换普通证明文件后重新提交审核</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>文件替换</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>替换普通证明文件后重新提交审核</t>
+          <t>在 Fidère 客户端验证：替换普通证明文件后重新提交审核</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>修改资料和替换文件可一并重新提交审核</t>
+          <t>修改资料和替换文件可一并重新提交审核；当前原型未完整体现重新提交链路，原型待补充</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>当前原型未完整体现重新提交链路，原型待补充</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -937,22 +851,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>FATCA 签署 - FATCA 未签署时提交开户申请</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FATCA 签署</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FATCA 未签署时提交开户申请</t>
+          <t>在 Fidère 客户端验证：FATCA 未签署时提交开户申请</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,11 +875,6 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -979,22 +888,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>FATCA 签署 - 完成 FATCA 第三方签署</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FATCA 签署</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>完成 FATCA 第三方签署</t>
+          <t>在 Fidère 客户端验证：完成 FATCA 第三方签署</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1003,11 +912,6 @@
         </is>
       </c>
       <c r="G19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1021,35 +925,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>FATCA 签署 - 已签署 FATCA 尝试通过普通上传覆盖</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FATCA 签署</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>已签署 FATCA 尝试通过普通上传覆盖</t>
+          <t>在 Fidère 客户端验证：已签署 FATCA 尝试通过普通上传覆盖</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>已签署 FATCA 不会被普通上传文件直接覆盖</t>
+          <t>已签署 FATCA 不会被普通上传文件直接覆盖；原型待补充</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
-        <is>
-          <t>原型待补充</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1063,35 +962,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>FATCA 重新签署 - 修改内容影响签署文件后重新生成待签署版本</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FATCA 重新签署</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>修改内容影响签署文件后重新生成待签署版本</t>
+          <t>在 Fidère 客户端验证：修改内容影响签署文件后重新生成待签署版本</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>系统生成新的待签署版本并允许重新签署</t>
+          <t>系统生成新的待签署版本并允许重新签署；原型待补充</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
-        <is>
-          <t>原型待补充</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1105,35 +999,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>FATCA 历史版本 - 查看原已签署 FATCA 历史版本</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FATCA 历史版本</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>查看原已签署 FATCA 历史版本</t>
+          <t>在 Fidère 客户端验证：查看原已签署 FATCA 历史版本</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>历史已签署版本可保留并查看</t>
+          <t>历史已签署版本可保留并查看；原型待补充</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>原型待补充</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1147,22 +1036,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>开户审核列表 - 管理端列表收到客户端提交的开户申请</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>开户审核列表</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>管理端列表收到客户端提交的开户申请</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端列表收到客户端提交的开户申请</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1171,11 +1060,6 @@
         </is>
       </c>
       <c r="G23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1189,22 +1073,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>开户审核详情 - 进入开户申请详情</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>开户审核详情</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>进入开户申请详情</t>
+          <t>运营人工操作在 Fidère 管理端验证：进入开户申请详情</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1213,11 +1097,6 @@
         </is>
       </c>
       <c r="G24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1231,22 +1110,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>资料查看 - 管理端展示用户开户资料</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>资料查看</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>管理端展示用户开户资料</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端展示用户开户资料</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1255,11 +1134,6 @@
         </is>
       </c>
       <c r="G25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1273,22 +1147,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>文件查看 - 管理端查看普通证明文件</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>文件查看</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>管理端查看普通证明文件</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端查看普通证明文件</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1297,11 +1171,6 @@
         </is>
       </c>
       <c r="G26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1315,22 +1184,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>签署文件查看 - 管理端查看 FATCA 签署文件</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>签署文件查看</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>管理端查看 FATCA 签署文件</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端查看 FATCA 签署文件</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1339,11 +1208,6 @@
         </is>
       </c>
       <c r="G27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1357,22 +1221,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>开户审核 - 管理端审核通过开户申请</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>开户审核</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>管理端审核通过开户申请</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端审核通过开户申请</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1381,11 +1245,6 @@
         </is>
       </c>
       <c r="G28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1399,22 +1258,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>开户审核 - 管理端审核拒绝开户申请</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>开户审核</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>管理端审核拒绝开户申请</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端审核拒绝开户申请</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1423,11 +1282,6 @@
         </is>
       </c>
       <c r="G29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1441,35 +1295,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>拒绝原因 - 审核拒绝时不填写拒绝原因</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>拒绝原因</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>审核拒绝时不填写拒绝原因</t>
+          <t>运营人工操作在 Fidère 管理端验证：审核拒绝时不填写拒绝原因</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>系统按规则拦截或记录为空风险</t>
+          <t>系统按规则拦截或记录为空风险；拒绝原因是否必填待确认</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
-        <is>
-          <t>拒绝原因是否必填待确认</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1483,22 +1332,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>拒绝原因 - 审核拒绝后客户端查看原因</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>拒绝原因</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>审核拒绝后客户端查看原因</t>
+          <t>运营人工操作在 Fidère 管理端验证：审核拒绝后客户端查看原因</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1507,11 +1356,6 @@
         </is>
       </c>
       <c r="G31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1525,35 +1369,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>资料更新 - 用户修改资料重新提交后管理端查看资料</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>资料更新</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>用户修改资料重新提交后管理端查看资料</t>
+          <t>运营人工操作在 Fidère 管理端验证：用户修改资料重新提交后管理端查看资料</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>管理端展示最新资料和更新后的文件</t>
+          <t>管理端展示最新资料和更新后的文件；原型待补充</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>原型待补充</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1567,22 +1406,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>管理端</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>BaaS 提交前置 - 管理端未审核通过时检查是否提交 BaaS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BaaS 提交前置</t>
+          <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>管理端未审核通过时检查是否提交 BaaS</t>
+          <t>运营人工操作在 Fidère 管理端验证：管理端未审核通过时检查是否提交 BaaS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1591,11 +1430,6 @@
         </is>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1609,22 +1443,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>开户提交 - 仅管理端审核通过后触发提交 BaaS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>开户提交</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>仅管理端审核通过后触发提交 BaaS</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：仅管理端审核通过后触发提交 BaaS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1633,11 +1467,6 @@
         </is>
       </c>
       <c r="G34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1651,22 +1480,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>开户提交 - 提交 BaaS 的用户资料与管理端审核资料一致</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>开户提交</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>提交 BaaS 的用户资料与管理端审核资料一致</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：提交 BaaS 的用户资料与管理端审核资料一致</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1675,11 +1504,6 @@
         </is>
       </c>
       <c r="G35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1693,22 +1517,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>开户提交 - 提交 BaaS 后客户端和管理端查看处理中状态</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>开户提交</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>提交 BaaS 后客户端和管理端查看处理中状态</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：提交 BaaS 后客户端和管理端查看处理中状态</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1717,11 +1541,6 @@
         </is>
       </c>
       <c r="G36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1735,22 +1554,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>资金权限 - 开户处理中时进入美国账户资金功能</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>资金权限</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>开户处理中时进入美国账户资金功能</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：开户处理中时进入美国账户资金功能</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1759,11 +1578,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1777,22 +1591,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>开户成功 - BaaS 返回开户成功后管理端状态更新</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>开户成功</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BaaS 返回开户成功后管理端状态更新</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回开户成功后管理端状态更新</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1801,11 +1615,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1819,22 +1628,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>开户成功 - BaaS 返回开户成功后客户端状态更新</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>开户成功</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BaaS 返回开户成功后客户端状态更新</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回开户成功后客户端状态更新</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1843,11 +1652,6 @@
         </is>
       </c>
       <c r="G39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1861,22 +1665,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>账户信息 - 开户成功后客户端展示美国账户信息</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>账户信息</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>开户成功后客户端展示美国账户信息</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：开户成功后客户端展示美国账户信息</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1885,11 +1689,6 @@
         </is>
       </c>
       <c r="G40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1903,22 +1702,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>资金权限 - 开户成功后进入美国账户入金入口</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>资金权限</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>开户成功后进入美国账户入金入口</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：开户成功后进入美国账户入金入口</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1927,11 +1726,6 @@
         </is>
       </c>
       <c r="G41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1945,22 +1739,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>资金权限 - 开户成功后进入美国账户转出入口</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>资金权限</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>开户成功后进入美国账户转出入口</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：开户成功后进入美国账户转出入口</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1969,11 +1763,6 @@
         </is>
       </c>
       <c r="G42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1987,22 +1776,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>开户失败 - BaaS 返回开户失败后客户端和管理端查看状态</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>开户失败</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BaaS 返回开户失败后客户端和管理端查看状态</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回开户失败后客户端和管理端查看状态</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2011,11 +1800,6 @@
         </is>
       </c>
       <c r="G43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2029,35 +1813,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>拒绝原因 - BaaS 返回拒绝原因后页面展示</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>拒绝原因</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BaaS 返回拒绝原因后页面展示</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回拒绝原因后页面展示</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>客户端或管理端展示对应拒绝原因</t>
+          <t>客户端或管理端展示对应拒绝原因；状态文案和原因展示位置待确认</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
-        <is>
-          <t>状态文案和原因展示位置待确认</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2071,22 +1850,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>BaaS 对接</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BaaS 对接</t>
+          <t>资金权限 - 开户失败或拒绝后进入资金功能</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>资金权限</t>
+          <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>开户失败或拒绝后进入资金功能</t>
+          <t>在 Fidère 管理端/BaaS 平台验证：开户失败或拒绝后进入资金功能</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2095,11 +1874,6 @@
         </is>
       </c>
       <c r="G45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2113,35 +1887,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>美国账户展示 - 核对美国账户展示字段</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>美国账户展示</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>核对美国账户展示字段</t>
+          <t>在 Fidère 客户端验证：核对美国账户展示字段</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>字段与 PRD/原型一致，不展示后台敏感信息</t>
+          <t>字段与 PRD/原型一致，不展示后台敏感信息；具体字段待确认</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
-        <is>
-          <t>具体字段待确认</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2155,22 +1924,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>账户区分 - 查看美国账户和香港账户入口</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>账户区分</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>查看美国账户和香港账户入口</t>
+          <t>在 Fidère 客户端验证：查看美国账户和香港账户入口</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2179,11 +1948,6 @@
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2197,22 +1961,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>账户区分 - 查看美国账户和香港账户账户信息</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>账户区分</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>查看美国账户和香港账户账户信息</t>
+          <t>在 Fidère 客户端验证：查看美国账户和香港账户账户信息</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2221,11 +1985,6 @@
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2239,22 +1998,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>交易记录 - 查看美国账户和香港账户交易记录</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>交易记录</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>查看美国账户和香港账户交易记录</t>
+          <t>在 Fidère 客户端验证：查看美国账户和香港账户交易记录</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2263,11 +2022,6 @@
         </is>
       </c>
       <c r="G49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2281,22 +2035,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>客户端</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>客户端</t>
+          <t>资金权限 - 待审核、处理中、失败或拒绝状态下操作美国账户资金功能</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>资金权限</t>
+          <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>待审核、处理中、失败或拒绝状态下操作美国账户资金功能</t>
+          <t>在 Fidère 客户端验证：待审核、处理中、失败或拒绝状态下操作美国账户资金功能</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2305,11 +2059,6 @@
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2323,35 +2072,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>线下转账 - BaaS 生成线下转账对应入金记录</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>线下转账</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BaaS 生成线下转账对应入金记录</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：BaaS 生成线下转账对应入金记录</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BaaS 平台存在对应入金记录</t>
+          <t>BaaS 平台存在对应入金记录；需外部 BaaS 测试环境支持</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
-        <is>
-          <t>需外部 BaaS 测试环境支持</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2365,22 +2109,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>BaaS 记录查看 - 运营查看 BaaS 入金记录</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BaaS 记录查看</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>运营查看 BaaS 入金记录</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营查看 BaaS 入金记录</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2389,11 +2133,6 @@
         </is>
       </c>
       <c r="G52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2407,22 +2146,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金入口 - Fidère 管理端存在手动入金入口</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>手动入金入口</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fidère 管理端存在手动入金入口</t>
+          <t>在 Fidère 客户端验证：Fidère 管理端存在手动入金入口</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2431,11 +2170,6 @@
         </is>
       </c>
       <c r="G53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2449,22 +2183,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金 - 手动入金选择美国账户用户</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>手动入金</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>手动入金选择美国账户用户</t>
+          <t>在 Fidère 客户端验证：手动入金选择美国账户用户</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2473,11 +2207,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2491,22 +2220,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金 - 手动入金选择正确币种并输入有效金额</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>手动入金</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>手动入金选择正确币种并输入有效金额</t>
+          <t>在 Fidère 客户端验证：手动入金选择正确币种并输入有效金额</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2515,11 +2244,6 @@
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2533,22 +2257,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金校验 - 用户或账户未选择时提交手动入金</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>手动入金校验</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>用户或账户未选择时提交手动入金</t>
+          <t>在 Fidère 客户端验证：用户或账户未选择时提交手动入金</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2557,11 +2281,6 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2575,22 +2294,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金校验 - 金额为空时提交手动入金</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>手动入金校验</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>金额为空时提交手动入金</t>
+          <t>在 Fidère 客户端验证：金额为空时提交手动入金</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2599,11 +2318,6 @@
         </is>
       </c>
       <c r="G57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2617,22 +2331,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金校验 - 金额为 0、负数或非法格式时提交</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>手动入金校验</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>金额为 0、负数或非法格式时提交</t>
+          <t>在 Fidère 客户端验证：金额为 0、负数或非法格式时提交</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2641,11 +2355,6 @@
         </is>
       </c>
       <c r="G58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2659,22 +2368,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>手动入金提交 - 运营提交有效手动入金</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>手动入金提交</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>运营提交有效手动入金</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营提交有效手动入金</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2683,11 +2392,6 @@
         </is>
       </c>
       <c r="G59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2701,22 +2405,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>管理端记录 - 手动入金成功后查看管理端记录</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>管理端记录</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>手动入金成功后查看管理端记录</t>
+          <t>在 Fidère 客户端验证：手动入金成功后查看管理端记录</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2725,11 +2429,6 @@
         </is>
       </c>
       <c r="G60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2743,35 +2442,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>客户端记录 - 手动入金成功后客户端查看余额或记录</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>客户端记录</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>手动入金成功后客户端查看余额或记录</t>
+          <t>在 Fidère 客户端验证：手动入金成功后客户端查看余额或记录</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>客户端展示对应入金记录或余额变化</t>
+          <t>客户端展示对应入金记录或余额变化；余额更新时间和记录生成时机待确认</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
-        <is>
-          <t>余额更新时间和记录生成时机待确认</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2785,35 +2479,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>数据核对 - 核对 Fidère 手动入金记录与 BaaS 入金记录</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>数据核对</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>核对 Fidère 手动入金记录与 BaaS 入金记录</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：核对 Fidère 手动入金记录与 BaaS 入金记录</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>两侧记录可通过金额、币种、账户、时间或编号核对</t>
+          <t>两侧记录可通过金额、币种、账户、时间或编号核对；核对字段待确认/原型待补充</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
-        <is>
-          <t>核对字段待确认/原型待补充</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2827,22 +2516,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金入口 - 已开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>入金入口</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>已开户成功用户进入美国账户入金申请页</t>
+          <t>在 Fidère 客户端验证：已开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2851,11 +2540,6 @@
         </is>
       </c>
       <c r="G63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2869,22 +2553,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金权限 - 未开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>入金权限</t>
+          <t>用户美国账户未最终开户成功。</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>未开户成功用户进入美国账户入金申请页</t>
+          <t>在 Fidère 客户端验证：未开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2893,11 +2577,6 @@
         </is>
       </c>
       <c r="G64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2911,22 +2590,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>账户类型 - 入金申请页展示美国账户类型并展示或选择入金币种</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>账户类型</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>入金申请页展示美国账户类型并展示或选择入金币种</t>
+          <t>在 Fidère 客户端验证：入金申请页展示美国账户类型并展示或选择入金币种</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2935,11 +2614,6 @@
         </is>
       </c>
       <c r="G65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2953,22 +2627,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金提交 - 提交有效入金金额</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>入金提交</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>提交有效入金金额</t>
+          <t>在 Fidère 客户端验证：提交有效入金金额</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2977,11 +2651,6 @@
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2995,22 +2664,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金校验 - 金额为空、0、负数或非法格式时提交入金申请</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>入金校验</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>金额为空、0、负数或非法格式时提交入金申请</t>
+          <t>在 Fidère 客户端验证：金额为空、0、负数或非法格式时提交入金申请</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3019,11 +2688,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3037,22 +2701,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金状态 - 客户端提交入金申请后查看状态</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>入金状态</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>客户端提交入金申请后查看状态</t>
+          <t>在 Fidère 客户端验证：客户端提交入金申请后查看状态</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3061,11 +2725,6 @@
         </is>
       </c>
       <c r="G68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3079,22 +2738,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>管理端记录 - 管理端收到对应待审核入金申请</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>管理端记录</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>管理端收到对应待审核入金申请</t>
+          <t>在 Fidère 客户端验证：管理端收到对应待审核入金申请</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3103,11 +2762,6 @@
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3121,35 +2775,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>BaaS 录入依据 - 查看管理端入金申请信息是否足够 BaaS 录入</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BaaS 录入依据</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>查看管理端入金申请信息是否足够 BaaS 录入</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：查看管理端入金申请信息是否足够 BaaS 录入</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>申请信息足以供运营人工在 BaaS 平台核对和录入</t>
+          <t>申请信息足以供运营人工在 BaaS 平台核对和录入；核对字段待确认/原型待补充</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>核对字段待确认/原型待补充</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3163,35 +2812,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>BaaS 人工录入 - 运营在 BaaS 平台人工录入对应入金数据</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BaaS 人工录入</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>运营在 BaaS 平台人工录入对应入金数据</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营在 BaaS 平台人工录入对应入金数据</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BaaS 平台录入成功</t>
+          <t>BaaS 平台录入成功；需外部 BaaS 测试环境支持</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
-        <is>
-          <t>需外部 BaaS 测试环境支持</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3205,22 +2849,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金审核 - BaaS 录入完成后管理端审核通过入金申请</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>入金审核</t>
+          <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BaaS 录入完成后管理端审核通过入金申请</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：BaaS 录入完成后管理端审核通过入金申请</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3229,11 +2873,6 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3247,22 +2886,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>状态同步 - 管理端审核通过后客户端查看入金状态</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>状态同步</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>管理端审核通过后客户端查看入金状态</t>
+          <t>在 Fidère 客户端验证：管理端审核通过后客户端查看入金状态</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3271,11 +2910,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3289,35 +2923,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>资金结果 - 管理端审核通过后查看余额或交易记录</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>资金结果</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>管理端审核通过后查看余额或交易记录</t>
+          <t>在 Fidère 客户端验证：管理端审核通过后查看余额或交易记录</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>客户端和管理端展示正确余额或交易记录</t>
+          <t>客户端和管理端展示正确余额或交易记录；余额变化规则待确认</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
-        <is>
-          <t>余额变化规则待确认</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3331,22 +2960,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户入金</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>美国账户入金</t>
+          <t>入金拒绝 - 管理端拒绝入金申请</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>入金拒绝</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>管理端拒绝入金申请</t>
+          <t>在 Fidère 客户端验证：管理端拒绝入金申请</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3355,11 +2984,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3373,22 +2997,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出入口 - 已开户成功用户进入美国账户转出页</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>转出入口</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>已开户成功用户进入美国账户转出页</t>
+          <t>在 Fidère 客户端验证：已开户成功用户进入美国账户转出页</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3397,11 +3021,6 @@
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3415,22 +3034,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出权限 - 未开户成功用户进入美国账户转出页</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>转出权限</t>
+          <t>用户美国账户未最终开户成功。</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>未开户成功用户进入美国账户转出页</t>
+          <t>在 Fidère 客户端验证：未开户成功用户进入美国账户转出页</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3439,11 +3058,6 @@
         </is>
       </c>
       <c r="G77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3457,22 +3071,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>账户类型 - 转出页展示转出账户</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>账户类型</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>转出页展示转出账户</t>
+          <t>在 Fidère 客户端验证：转出页展示转出账户</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3481,11 +3095,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3499,22 +3108,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>收款人 - 选择/填写收款人、转出金额和转账用途</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>收款人</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>选择/填写收款人、转出金额和转账用途</t>
+          <t>在 Fidère 客户端验证：选择/填写收款人、转出金额和转账用途</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3523,11 +3132,6 @@
         </is>
       </c>
       <c r="G79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3541,22 +3145,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出校验 - 收款人、金额或转账用途缺失时提交转出</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>转出校验</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>收款人、金额或转账用途缺失时提交转出</t>
+          <t>在 Fidère 客户端验证：收款人、金额或转账用途缺失时提交转出</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3565,11 +3169,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3583,22 +3182,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出校验 - 金额为 0、负数或非法格式时提交转出</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>转出校验</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>金额为 0、负数或非法格式时提交转出</t>
+          <t>在 Fidère 客户端验证：金额为 0、负数或非法格式时提交转出</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3607,11 +3206,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3625,22 +3219,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>余额校验 - 余额不足时提交转出申请</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>余额校验</t>
+          <t>用户美国账户已最终开户成功但可用余额不足。</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>余额不足时提交转出申请</t>
+          <t>在 Fidère 客户端验证：余额不足时提交转出申请</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3649,11 +3243,6 @@
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3667,22 +3256,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出提交 - 提交有效美国账户转出申请</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>转出提交</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>提交有效美国账户转出申请</t>
+          <t>在 Fidère 客户端验证：提交有效美国账户转出申请</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3691,11 +3280,6 @@
         </is>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3709,22 +3293,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>管理端记录 - 管理端查看待审核转出数据</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>管理端记录</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>管理端查看待审核转出数据</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端查看待审核转出数据</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3733,11 +3317,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3751,35 +3330,30 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>BaaS 创建依据 - 查看管理端转出信息是否足够 BaaS 创建转出</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BaaS 创建依据</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>查看管理端转出信息是否足够 BaaS 创建转出</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：查看管理端转出信息是否足够 BaaS 创建转出</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>信息足以供运营人工在 BaaS 平台创建对应转出</t>
+          <t>信息足以供运营人工在 BaaS 平台创建对应转出；核对字段待确认/原型待补充</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>核对字段待确认/原型待补充</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3793,35 +3367,30 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>BaaS 人工转出 - 运营在 BaaS 平台人工创建对应转出</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BaaS 人工转出</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>运营在 BaaS 平台人工创建对应转出</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营在 BaaS 平台人工创建对应转出</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BaaS 平台转出创建成功</t>
+          <t>BaaS 平台转出创建成功；需外部 BaaS 测试环境支持</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>需外部 BaaS 测试环境支持</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3835,22 +3404,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出审核 - BaaS 转出完成且确认到账后管理端审核通过</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>转出审核</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BaaS 转出完成且确认到账后管理端审核通过</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：BaaS 转出完成且确认到账后管理端审核通过</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3859,11 +3428,6 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3877,22 +3441,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>状态同步 - 管理端审核通过后客户端查看转出状态</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>状态同步</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>管理端审核通过后客户端查看转出状态</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端审核通过后客户端查看转出状态</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3901,11 +3465,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3919,35 +3478,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>资金结果 - 管理端审核通过后查看交易记录或余额</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>资金结果</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>管理端审核通过后查看交易记录或余额</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端审核通过后查看交易记录或余额</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>客户端和管理端展示正确交易记录或余额变化</t>
+          <t>客户端和管理端展示正确交易记录或余额变化；冻结、扣减和到账金额规则待确认</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>冻结、扣减和到账金额规则待确认</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3961,22 +3515,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出拒绝 - 管理端拒绝转出申请</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>转出拒绝</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>管理端拒绝转出申请</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端拒绝转出申请</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3985,11 +3539,6 @@
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4003,22 +3552,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出处理中 - 转出处于处理中时查看客户端和管理端状态</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>转出处理中</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>转出处于处理中时查看客户端和管理端状态</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：转出处于处理中时查看客户端和管理端状态</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4027,11 +3576,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4045,35 +3589,30 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>美国账户转出</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>美国账户转出</t>
+          <t>转出失败与核对 - 转出失败时核对 Fidère 申请与 BaaS 转出记录</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>转出失败与核对</t>
+          <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>转出失败时核对 Fidère 申请与 BaaS 转出记录</t>
+          <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：转出失败时核对 Fidère 申请与 BaaS 转出记录</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>失败状态展示正确，且两侧记录可核对</t>
+          <t>失败状态展示正确，且两侧记录可核对；失败后释放规则和核对字段待确认</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>失败后释放规则和核对字段待确认</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4087,22 +3626,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>账户查看 - 用户查看香港账户</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>账户查看</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>用户查看香港账户</t>
+          <t>在 Fidère 客户端/管理端验证：用户查看香港账户</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4111,11 +3650,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4129,22 +3663,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>转入入口 - 用户进入香港账户转入页</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>转入入口</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>用户进入香港账户转入页</t>
+          <t>在 Fidère 客户端/管理端验证：用户进入香港账户转入页</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4153,11 +3687,6 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4171,22 +3700,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>转入提交 - 提交香港账户转入申请</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>转入提交</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>提交香港账户转入申请</t>
+          <t>在 Fidère 客户端/管理端验证：提交香港账户转入申请</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4195,11 +3724,6 @@
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4213,22 +3737,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>转入结果 - 查看香港账户转入结果或交易记录</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>转入结果</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>查看香港账户转入结果或交易记录</t>
+          <t>在 Fidère 客户端/管理端验证：查看香港账户转入结果或交易记录</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4237,11 +3761,6 @@
         </is>
       </c>
       <c r="G96" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4255,22 +3774,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>转出入口 - 用户进入香港账户转出页</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>转出入口</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>用户进入香港账户转出页</t>
+          <t>在 Fidère 客户端/管理端验证：用户进入香港账户转出页</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4279,11 +3798,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4297,22 +3811,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>转出提交 - 提交香港账户转出申请</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>转出提交</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>提交香港账户转出申请</t>
+          <t>在 Fidère 客户端/管理端验证：提交香港账户转出申请</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4321,11 +3835,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4339,22 +3848,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>转出结果 - 查看香港账户转出结果或交易记录</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>转出结果</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>查看香港账户转出结果或交易记录</t>
+          <t>在 Fidère 客户端/管理端验证：查看香港账户转出结果或交易记录</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4363,11 +3872,6 @@
         </is>
       </c>
       <c r="G99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4381,22 +3885,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>入口区分 - 查看香港账户与美国账户转入/转出入口</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>入口区分</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>查看香港账户与美国账户转入/转出入口</t>
+          <t>在 Fidère 客户端/管理端验证：查看香港账户与美国账户转入/转出入口</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4405,11 +3909,6 @@
         </is>
       </c>
       <c r="G100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4423,22 +3922,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>香港账户回归</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>香港账户回归</t>
+          <t>记录区分 - 查看香港账户与美国账户交易记录或账户类型</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>记录区分</t>
+          <t>用户已具备香港账户。</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>查看香港账户与美国账户交易记录或账户类型</t>
+          <t>在 Fidère 客户端/管理端验证：查看香港账户与美国账户交易记录或账户类型</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4447,11 +3946,6 @@
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
+++ b/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
@@ -206,12 +206,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -222,30 +223,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>测试模块</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>第一轮实际结果</t>
         </is>
@@ -259,30 +265,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>开户入口 - 个人用户进入美国账户开户申请页</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：个人用户进入美国账户开户申请页</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>成功进入个人美国账户开户申请页，并展示个人开户流程入口</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -296,30 +307,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>开户入口 - 企业用户尝试进入个人美国账户开户流程</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>存在企业用户或非个人用户账号。</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：企业用户尝试进入个人美国账户开户流程</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>系统不允许进入个人美国账户开户流程，或展示不适用提示；当前原型存在企业开户切换入口，企业限制为原型待补充</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -333,30 +349,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>开户资料填写 - 开户申请页展示开户资料区域</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：开户申请页展示开户资料区域</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>页面展示个人资料、补充资料、证明文件和 FATCA 签署区域</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -370,30 +391,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>开户资料填写 - 开户必填字段为空时提交申请</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：开户必填字段为空时提交申请</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>系统阻止提交并展示明确必填提示</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -407,30 +433,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>开户资料填写 - 填写合法开户关键字段后继续下一步</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：填写合法开户关键字段后继续下一步</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>合法字段可保存或进入下一步，不出现校验错误</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -444,30 +475,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>开户资料填写 - 国家/地区、证件类型、出生日期等选择类字段正常选择</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：国家/地区、证件类型、出生日期等选择类字段正常选择</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>选择类字段可正常选择并展示正确值</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -481,30 +517,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>开户提交 - 资料和文件完整后提交美国账户开户申请</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：资料和文件完整后提交美国账户开户申请</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>开户申请提交成功，并进入待审核状态</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -518,30 +559,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>开户状态 - 开户申请提交成功后查看客户端状态</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：开户申请提交成功后查看客户端状态</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>客户端展示待审核/审核中状态，资金功能不可用</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -555,30 +601,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>文件上传 - 上传护照文件</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：上传护照文件</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>护照文件上传成功并展示文件名或已上传状态</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -592,30 +643,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>文件上传 - 上传身份证明文件</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：上传身份证明文件</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>身份证明文件上传成功并展示文件名或已上传状态</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -629,30 +685,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>文件上传 - 上传自拍照文件</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：上传自拍照文件</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>自拍照上传成功并展示文件名或已上传状态</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -666,30 +727,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>文件上传 - 上传地址证明文件</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：上传地址证明文件</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>地址证明上传成功并展示文件名或已上传状态</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -703,30 +769,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>文件上传 - 上传资金来源证明文件</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：上传资金来源证明文件</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>资金来源证明上传成功并展示文件名或已上传状态</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -740,30 +811,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>文件上传 - 缺少必填证明文件时提交开户申请</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：缺少必填证明文件时提交开户申请</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>系统阻止提交并提示缺少必填文件</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -777,30 +853,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>文件替换 - 普通证明文件替换为新文件</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：普通证明文件替换为新文件</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>替换成功，页面展示新文件名或更新状态</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -814,30 +895,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>文件替换 - 替换普通证明文件后重新提交审核</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：替换普通证明文件后重新提交审核</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>修改资料和替换文件可一并重新提交审核；当前原型未完整体现重新提交链路，原型待补充</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -851,30 +937,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>FATCA 签署 - FATCA 未签署时提交开户申请</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：FATCA 未签署时提交开户申请</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>系统阻止提交并提示需完成 FATCA 签署</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -888,30 +979,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>FATCA 签署 - 完成 FATCA 第三方签署</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：完成 FATCA 第三方签署</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>FATCA 状态更新为已签署</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -925,30 +1021,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>FATCA 签署 - 已签署 FATCA 尝试通过普通上传覆盖</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：已签署 FATCA 尝试通过普通上传覆盖</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>已签署 FATCA 不会被普通上传文件直接覆盖；原型待补充</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -962,30 +1063,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>FATCA 重新签署 - 修改内容影响签署文件后重新生成待签署版本</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：修改内容影响签署文件后重新生成待签署版本</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>系统生成新的待签署版本并允许重新签署；原型待补充</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -999,30 +1105,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>FATCA 历史版本 - 查看原已签署 FATCA 历史版本</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：查看原已签署 FATCA 历史版本</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>历史已签署版本可保留并查看；原型待补充</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1036,30 +1147,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>开户审核列表 - 管理端列表收到客户端提交的开户申请</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端列表收到客户端提交的开户申请</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>列表展示对应个人开户申请及审核状态</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1073,30 +1189,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>开户审核详情 - 进入开户申请详情</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：进入开户申请详情</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>可打开申请详情页并查看申请基础信息</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1110,30 +1231,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>资料查看 - 管理端展示用户开户资料</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端展示用户开户资料</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>用户资料字段展示完整且与客户端提交一致</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1147,30 +1273,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>文件查看 - 管理端查看普通证明文件</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端查看普通证明文件</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>普通证明文件可查看、下载或识别上传状态</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1184,30 +1315,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>签署文件查看 - 管理端查看 FATCA 签署文件</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端查看 FATCA 签署文件</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>FATCA 文件或签署状态可查看</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1221,30 +1357,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>开户审核 - 管理端审核通过开户申请</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端审核通过开户申请</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>申请状态变为审核通过，并进入提交 BaaS 前后状态</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1258,30 +1399,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>开户审核 - 管理端审核拒绝开户申请</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端审核拒绝开户申请</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>申请状态变为拒绝，客户端不可使用美国账户资金功能</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1295,30 +1441,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>拒绝原因 - 审核拒绝时不填写拒绝原因</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：审核拒绝时不填写拒绝原因</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>系统按规则拦截或记录为空风险；拒绝原因是否必填待确认</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1332,30 +1483,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>拒绝原因 - 审核拒绝后客户端查看原因</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：审核拒绝后客户端查看原因</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>客户端展示拒绝状态及对应原因</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1369,30 +1525,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>资料更新 - 用户修改资料重新提交后管理端查看资料</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：用户修改资料重新提交后管理端查看资料</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>管理端展示最新资料和更新后的文件；原型待补充</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1406,30 +1567,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>管理端</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>BaaS 提交前置 - 管理端未审核通过时检查是否提交 BaaS</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Fidère 客户端已提交个人美国账户开户申请。</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>运营人工操作在 Fidère 管理端验证：管理端未审核通过时检查是否提交 BaaS</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>未审核通过的申请不会提交至 Interlace/BaaS</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1443,30 +1609,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>开户提交 - 仅管理端审核通过后触发提交 BaaS</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：仅管理端审核通过后触发提交 BaaS</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>BaaS 提交动作只发生在管理端审核通过之后</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1480,30 +1651,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>开户提交 - 提交 BaaS 的用户资料与管理端审核资料一致</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：提交 BaaS 的用户资料与管理端审核资料一致</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>提交资料与审核通过资料一致</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1517,30 +1693,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>开户提交 - 提交 BaaS 后客户端和管理端查看处理中状态</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：提交 BaaS 后客户端和管理端查看处理中状态</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>客户端和管理端均展示开户处理中或等价状态</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1554,30 +1735,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>资金权限 - 开户处理中时进入美国账户资金功能</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：开户处理中时进入美国账户资金功能</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>客户端不能使用美国账户入金和转出</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1591,30 +1777,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>开户成功 - BaaS 返回开户成功后管理端状态更新</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回开户成功后管理端状态更新</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>管理端展示开户成功</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1628,30 +1819,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>开户成功 - BaaS 返回开户成功后客户端状态更新</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回开户成功后客户端状态更新</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>客户端展示开户成功</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1665,30 +1861,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>账户信息 - 开户成功后客户端展示美国账户信息</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：开户成功后客户端展示美国账户信息</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>客户端展示美国账户基础信息</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1702,30 +1903,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>资金权限 - 开户成功后进入美国账户入金入口</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：开户成功后进入美国账户入金入口</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>入金入口可用</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1739,30 +1945,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>资金权限 - 开户成功后进入美国账户转出入口</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：开户成功后进入美国账户转出入口</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>转出入口可用</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1776,30 +1987,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>开户失败 - BaaS 返回开户失败后客户端和管理端查看状态</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回开户失败后客户端和管理端查看状态</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>客户端和管理端均展示失败状态</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1813,30 +2029,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>拒绝原因 - BaaS 返回拒绝原因后页面展示</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：BaaS 返回拒绝原因后页面展示</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>客户端或管理端展示对应拒绝原因；状态文案和原因展示位置待确认</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1850,30 +2071,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>BaaS 对接</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>资金权限 - 开户失败或拒绝后进入资金功能</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Fidère 管理端已完成对应开户审核操作。</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>在 Fidère 管理端/BaaS 平台验证：开户失败或拒绝后进入资金功能</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>资金功能不开放</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1887,30 +2113,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>美国账户展示 - 核对美国账户展示字段</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：核对美国账户展示字段</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>字段与 PRD/原型一致，不展示后台敏感信息；具体字段待确认</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1924,30 +2155,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>账户区分 - 查看美国账户和香港账户入口</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：查看美国账户和香港账户入口</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>两个账户入口清晰区分</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1961,30 +2197,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>账户区分 - 查看美国账户和香港账户账户信息</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：查看美国账户和香港账户账户信息</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>账户信息按账户类型正确区分</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1998,30 +2239,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>交易记录 - 查看美国账户和香港账户交易记录</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：查看美国账户和香港账户交易记录</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>交易记录可按账户类型区分</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2035,30 +2281,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>客户端</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>资金权限 - 待审核、处理中、失败或拒绝状态下操作美国账户资金功能</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>存在个人用户账号，进入 Fidère 客户端。</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：待审核、处理中、失败或拒绝状态下操作美国账户资金功能</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>入金和转出均不可操作</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2072,30 +2323,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>线下转账 - BaaS 生成线下转账对应入金记录</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：BaaS 生成线下转账对应入金记录</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>BaaS 平台存在对应入金记录；需外部 BaaS 测试环境支持</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2109,30 +2365,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>BaaS 记录查看 - 运营查看 BaaS 入金记录</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营查看 BaaS 入金记录</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>运营可看到用户、账户、金额、币种、时间或编号</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2146,30 +2407,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>手动入金入口 - Fidère 管理端存在手动入金入口</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：Fidère 管理端存在手动入金入口</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>管理端可进入手动入金功能</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2183,30 +2449,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>手动入金 - 手动入金选择美国账户用户</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：手动入金选择美国账户用户</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>可选择正确美国账户用户</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2220,30 +2491,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>手动入金 - 手动入金选择正确币种并输入有效金额</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：手动入金选择正确币种并输入有效金额</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>币种可选择或正确展示，有效金额可输入并保留</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2257,30 +2533,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>手动入金校验 - 用户或账户未选择时提交手动入金</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：用户或账户未选择时提交手动入金</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>系统阻止提交并提示选择用户或账户</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2294,30 +2575,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>手动入金校验 - 金额为空时提交手动入金</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：金额为空时提交手动入金</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>系统阻止提交并提示金额必填</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2331,30 +2617,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>手动入金校验 - 金额为 0、负数或非法格式时提交</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：金额为 0、负数或非法格式时提交</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>系统阻止提交并提示金额不合法</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2368,30 +2659,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>手动入金提交 - 运营提交有效手动入金</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营提交有效手动入金</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>手动入金提交成功</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2405,30 +2701,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>管理端记录 - 手动入金成功后查看管理端记录</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：手动入金成功后查看管理端记录</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>管理端生成对应入金记录或流水</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2442,30 +2743,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>客户端记录 - 手动入金成功后客户端查看余额或记录</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：手动入金成功后客户端查看余额或记录</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>客户端展示对应入金记录或余额变化；余额更新时间和记录生成时机待确认</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2479,30 +2785,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>数据核对 - 核对 Fidère 手动入金记录与 BaaS 入金记录</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：核对 Fidère 手动入金记录与 BaaS 入金记录</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>两侧记录可通过金额、币种、账户、时间或编号核对；核对字段待确认/原型待补充</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2516,30 +2827,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>入金入口 - 已开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：已开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>用户可进入美国账户入金申请页</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2553,30 +2869,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>入金权限 - 未开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>用户美国账户未最终开户成功。</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：未开户成功用户进入美国账户入金申请页</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>系统不允许进入或禁用入口</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2590,30 +2911,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>账户类型 - 入金申请页展示美国账户类型并展示或选择入金币种</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：入金申请页展示美国账户类型并展示或选择入金币种</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>账户类型展示为美国账户，币种可选择或正确展示</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2627,30 +2953,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>入金提交 - 提交有效入金金额</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：提交有效入金金额</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>客户端提交成功</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2664,30 +2995,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>入金校验 - 金额为空、0、负数或非法格式时提交入金申请</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：金额为空、0、负数或非法格式时提交入金申请</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>系统阻止提交并提示金额不合法或必填</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2701,30 +3037,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>入金状态 - 客户端提交入金申请后查看状态</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：客户端提交入金申请后查看状态</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>申请状态为待审核/UNDER_REVIEW</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2738,30 +3079,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>管理端记录 - 管理端收到对应待审核入金申请</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：管理端收到对应待审核入金申请</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>管理端展示该笔待审核入金申请</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2775,30 +3121,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>BaaS 录入依据 - 查看管理端入金申请信息是否足够 BaaS 录入</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：查看管理端入金申请信息是否足够 BaaS 录入</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>申请信息足以供运营人工在 BaaS 平台核对和录入；核对字段待确认/原型待补充</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2812,30 +3163,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>BaaS 人工录入 - 运营在 BaaS 平台人工录入对应入金数据</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营在 BaaS 平台人工录入对应入金数据</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>BaaS 平台录入成功；需外部 BaaS 测试环境支持</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2849,30 +3205,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>入金审核 - BaaS 录入完成后管理端审核通过入金申请</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功，且存在对应入金业务数据。</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：BaaS 录入完成后管理端审核通过入金申请</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>管理端可审核通过该入金申请</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2886,30 +3247,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>状态同步 - 管理端审核通过后客户端查看入金状态</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：管理端审核通过后客户端查看入金状态</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>客户端状态更新为已通过/已完成</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2923,30 +3289,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>资金结果 - 管理端审核通过后查看余额或交易记录</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：管理端审核通过后查看余额或交易记录</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>客户端和管理端展示正确余额或交易记录；余额变化规则待确认</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2960,30 +3331,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>美国账户入金</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>入金拒绝 - 管理端拒绝入金申请</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：管理端拒绝入金申请</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>客户端展示拒绝状态及原因</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2997,30 +3373,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>转出入口 - 已开户成功用户进入美国账户转出页</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：已开户成功用户进入美国账户转出页</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>用户可进入美国账户转出页</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3034,30 +3415,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>转出权限 - 未开户成功用户进入美国账户转出页</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>用户美国账户未最终开户成功。</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：未开户成功用户进入美国账户转出页</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>系统不允许进入或禁用入口</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3071,30 +3457,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>账户类型 - 转出页展示转出账户</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：转出页展示转出账户</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>转出账户展示为美国账户</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3108,30 +3499,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>收款人 - 选择/填写收款人、转出金额和转账用途</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：选择/填写收款人、转出金额和转账用途</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>收款人、金额和用途均可正常填写或选择</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3145,30 +3541,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>转出校验 - 收款人、金额或转账用途缺失时提交转出</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：收款人、金额或转账用途缺失时提交转出</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>系统阻止提交并提示对应必填项</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3182,30 +3583,35 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>转出校验 - 金额为 0、负数或非法格式时提交转出</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：金额为 0、负数或非法格式时提交转出</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>系统阻止提交并提示金额不合法</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3219,30 +3625,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>余额校验 - 余额不足时提交转出申请</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功但可用余额不足。</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：余额不足时提交转出申请</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>系统阻止提交，不生成可执行转出申请</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3256,30 +3667,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>转出提交 - 提交有效美国账户转出申请</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>在 Fidère 客户端验证：提交有效美国账户转出申请</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>客户端提交成功并生成转出申请</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3293,30 +3709,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>管理端记录 - 管理端查看待审核转出数据</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端查看待审核转出数据</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>管理端生成对应待审核转出数据</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3330,30 +3751,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>BaaS 创建依据 - 查看管理端转出信息是否足够 BaaS 创建转出</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：查看管理端转出信息是否足够 BaaS 创建转出</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>信息足以供运营人工在 BaaS 平台创建对应转出；核对字段待确认/原型待补充</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3367,30 +3793,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>BaaS 人工转出 - 运营在 BaaS 平台人工创建对应转出</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：运营在 BaaS 平台人工创建对应转出</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>BaaS 平台转出创建成功；需外部 BaaS 测试环境支持</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3404,30 +3835,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>转出审核 - BaaS 转出完成且确认到账后管理端审核通过</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：BaaS 转出完成且确认到账后管理端审核通过</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>管理端可审核通过该笔转出</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3441,30 +3877,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>状态同步 - 管理端审核通过后客户端查看转出状态</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端审核通过后客户端查看转出状态</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>客户端状态更新为已完成/审核通过</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3478,30 +3919,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>资金结果 - 管理端审核通过后查看交易记录或余额</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端审核通过后查看交易记录或余额</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>客户端和管理端展示正确交易记录或余额变化；冻结、扣减和到账金额规则待确认</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3515,30 +3961,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>转出拒绝 - 管理端拒绝转出申请</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：管理端拒绝转出申请</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>客户端展示拒绝状态及原因</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3552,30 +4003,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>转出处理中 - 转出处于处理中时查看客户端和管理端状态</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：转出处于处理中时查看客户端和管理端状态</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>客户端和管理端展示处理中状态</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3589,30 +4045,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>美国账户转出</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>转出失败与核对 - 转出失败时核对 Fidère 申请与 BaaS 转出记录</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>用户美国账户已最终开户成功。</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>运营人工操作在 BaaS 平台或 Fidère 管理端验证：转出失败时核对 Fidère 申请与 BaaS 转出记录</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>失败状态展示正确，且两侧记录可核对；失败后释放规则和核对字段待确认</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3626,30 +4087,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>账户查看 - 用户查看香港账户</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：用户查看香港账户</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>香港账户可正常展示</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3663,30 +4129,35 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>转入入口 - 用户进入香港账户转入页</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：用户进入香港账户转入页</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>香港账户转入入口可正常进入</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3700,30 +4171,35 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>转入提交 - 提交香港账户转入申请</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：提交香港账户转入申请</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>香港账户转入申请可正常提交</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3737,30 +4213,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>转入结果 - 查看香港账户转入结果或交易记录</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：查看香港账户转入结果或交易记录</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>转入结果或交易记录展示正常</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3774,30 +4255,35 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>转出入口 - 用户进入香港账户转出页</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：用户进入香港账户转出页</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>香港账户转出入口可正常进入</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3811,30 +4297,35 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>转出提交 - 提交香港账户转出申请</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：提交香港账户转出申请</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>香港账户转出申请可正常提交</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3848,30 +4339,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>转出结果 - 查看香港账户转出结果或交易记录</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：查看香港账户转出结果或交易记录</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>转出结果或交易记录展示正常</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3885,30 +4381,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>入口区分 - 查看香港账户与美国账户转入/转出入口</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：查看香港账户与美国账户转入/转出入口</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>两个账户的转入和转出入口均不混淆</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3922,30 +4423,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
           <t>香港账户回归</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>记录区分 - 查看香港账户与美国账户交易记录或账户类型</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>用户已具备香港账户。</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>在 Fidère 客户端/管理端验证：查看香港账户与美国账户交易记录或账户类型</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>交易记录或账户类型不混淆</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
+++ b/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
@@ -7,6 +7,7 @@
     <sheet name="P0清单" sheetId="3" r:id="rId3"/>
     <sheet name="测试数据" sheetId="4" r:id="rId4"/>
     <sheet name="统计" sheetId="5" r:id="rId5"/>
+    <sheet name="AI自动执行清单" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -79,7 +80,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B38"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -433,6 +434,67 @@
       <c r="B32" t="inlineStr">
         <is>
           <t>美国账户入金、转出和账户互转的余额更新时间、交易记录生成时机、Fidère 与 BaaS 核对字段仍需确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI 执行结果输出要求</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>实际执行用例</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>输出实际执行的用例编号，并逐条记录 PASS / FAIL / BLOCKED。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FAIL 证据</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FAIL 用例需保存失败截图，记录实际结果、预期结果、复现路径、页面错误提示；如可获取，记录控制台报错或失败请求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BLOCKED 说明</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BLOCKED 用例需记录阻塞原因，例如缺少测试账号、缺少 BaaS 测试环境、未提供模拟回调、产品规则未确认、原型未实现对应入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>执行总结</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>输出共执行多少条、PASS 多少条、FAIL 多少条、BLOCKED 多少条，以及是否存在阻断上线的 P0 问题。</t>
         </is>
       </c>
     </row>
@@ -12291,4 +12353,4864 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L75"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>是否可自动执行</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>执行端</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>功能模块</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>测试场景</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>测试账号/数据</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>操作步骤</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>预期结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t>失败证据要求</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t>执行结果</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t>阻塞原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>个人用户进入美国账户开户申请页</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>未申请美国账户的个人用户；可使用原型默认数据。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/opening。
+2. 点击美国账户开户申请入口或“创建/继续填写开户申请”。
+3. 进入 /admin/product-manual/baas-prototype/account-opening/create。
+4. 检查页面标题和开户申请区域。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>页面展示“BaaS 开户申请”或等价标题，并展示开户资料区域。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>必填字段缺失时无法提交</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>未申请美国账户的个人用户；使用原型默认表单。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 清空至少一个页面可编辑必填字段。
+3. 点击“提交开户申请”。
+4. 查看字段提示或待补清单。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并展示缺失必填项提示。</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>上传护照文件</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>待开发提供可上传的测试护照文件，例如 PDF/PNG/JPEG。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 定位护照文件上传区域。
+3. 上传测试护照文件。
+4. 查看文件名或上传状态。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>护照文件上传成功，页面展示文件名或上传成功状态。</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>缺少测试文件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>上传地址证明文件</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>待开发提供地址证明测试文件。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 定位地址证明上传区域。
+3. 上传测试地址证明文件。
+4. 查看文件名或上传状态。</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>地址证明上传成功，页面展示文件名或上传成功状态。</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>缺少测试文件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FATCA 未签署时不可完成提交</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FATCA 状态为未签署的个人用户或可模拟未签署状态。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 保持 FATCA/第三方签署状态为未签署。
+3. 填写其他必填信息。
+4. 点击“提交开户申请”。</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示需先完成第三方签署。</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>缺少未签署状态账号或模拟状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>需人工执行</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>完成 FATCA 第三方签署后状态展示</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>可进入真实或测试第三方签署流程的个人用户。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 点击 FATCA/第三方签署入口。
+3. 人工完成第三方签署。
+4. 返回开户申请页查看签署状态。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>签署状态更新为已签署，页面允许继续开户提交。</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>真实第三方签署流程无法由 AI 独立完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>完整资料提交开户申请</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>资料完整、文件齐全、签署完成且可扣费的个人用户。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 填写完整开户资料。
+3. 上传必填证明文件。
+4. 确认 FATCA 等签署完成。
+5. 点击“提交开户申请”。</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>开户申请提交成功，进入待审核或开户费已扣款后的审核状态。</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>缺少完整开户测试账号、测试文件或签署状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>提交成功后客户端展示待审核状态</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>已成功提交开户申请的个人用户。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1. 完成开户申请提交。
+2. 返回美国账户页面 /admin/product-manual/baas-prototype/opening。
+3. 查看美国账户状态卡片。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>客户端展示待审核/审核中状态，不展示开户成功态。</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>缺少已提交申请状态账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>美国账户开户申请</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>重复点击提交不会生成重复申请</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>可提交开户申请的个人用户，需能查看申请记录或状态变化。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 完成必填资料和签署。
+3. 连续点击“提交开户申请”两次。
+4. 查看页面状态、管理端申请列表或申请编号。</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>同一申请不会生成重复申请记录或重复状态流转。</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>待确认是否已有幂等控制；需可查看申请记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>美国账户开户费用扣费</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>开户页面展示开户费用</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>未申请美国账户的个人用户；使用原型默认数据。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/account-opening/create。
+2. 查看页面顶部或提交确认区域。
+3. 搜索开户费、USD 500、扣费提示等文案。</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>页面展示开户费用 USD 500、币种和扣费提示。</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>美国账户开户费用扣费</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>余额足够时扣费成功</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>余额大于或等于 USD 500 的个人用户。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1. 使用余额充足账号打开开户申请页。
+2. 完成资料、文件和签署。
+3. 点击“提交开户申请”。
+4. 查看扣费提示和提交结果。</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>开户费用扣费成功，可以继续后续开户申请流程。</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>缺少余额充足测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>美国账户开户费用扣费</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>扣费成功后余额减少</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>余额充足且可查看扣费前后余额的个人用户。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1. 记录提交前 USD 可用余额。
+2. 提交开户申请并触发扣费。
+3. 返回账户余额或交易记录页面。
+4. 对比扣费前后余额。</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>用户余额减少 USD 500，扣减金额与开户费用一致。</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>待确认扣费触发时点；缺少可查看余额的测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>美国账户开户费用扣费</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>扣费成功后生成开户费用交易记录</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>余额充足并完成开户费扣费的个人用户。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1. 完成开户申请提交并扣费成功。
+2. 点击“查看开户费交易记录”或进入交易记录。
+3. 查看最新费用记录。</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>新增开户费用交易记录，类型、金额 USD 500、币种和状态正确。</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>缺少已扣费状态账号或交易记录入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>美国账户开户费用扣费</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>余额不足时无法成功扣费</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>余额低于 USD 500 的个人用户。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1. 使用余额不足账号打开开户申请页。
+2. 完成资料、文件和签署。
+3. 点击“提交开户申请”。
+4. 查看扣费结果和余额。</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>系统提示余额不足，不扣减用户余额。</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>缺少余额不足测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>美国账户开户费用扣费</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>重复提交或重复确认不会重复扣费</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>余额充足且可查看交易记录的个人用户。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1. 完成开户资料。
+2. 连续点击提交/扣费确认两次。
+3. 查看余额变化和开户费交易记录数量。</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>同一笔开户申请仅产生一次有效扣费，不重复扣除余额。</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>需可查看余额和费用交易记录；待确认幂等规则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fidère 管理端开户审核</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>管理端查看客户端提交的开户申请</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>已由客户端提交的个人美国账户开户申请。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/admin-review。
+2. 在左侧选择“开户审核”。
+3. 查看开户申请列表。
+4. 搜索或定位对应用户申请。</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>列表出现对应开户申请，状态与客户端提交后状态一致。</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>缺少已提交申请记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fidère 管理端开户审核</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>管理端查看用户开户资料</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>已提交开户申请且资料完整的个人用户。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1. 进入管理端开户审核列表。
+2. 打开对应申请详情。
+3. 查看基本信息、个人信息、证件信息等字段。</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>管理端展示用户提交的个人开户资料。</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>缺少已提交申请记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fidère 管理端开户审核</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>管理端查看上传文件</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已提交开户申请且已上传普通证明文件的个人用户。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1. 打开管理端开户申请详情。
+2. 定位文件或附件区域。
+3. 点击查看护照、身份证明或地址证明文件。</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>普通证明文件可查看或下载。</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>缺少含附件的申请记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-040</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fidère 管理端开户审核</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>运营人工操作审核通过开户申请</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>待审核开户申请。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1. 打开管理端开户申请详情。
+2. 点击“开始处理”或进入审核操作区。
+3. 选择审核通过。
+4. 点击提交审核决定。</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>申请状态变更为审核通过，并进入提交 Interlace/BaaS 前后的后续状态。</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>缺少待审核申请记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fidère 管理端开户审核</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>运营人工操作审核拒绝并展示拒绝原因</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>待审核开户申请；需可填写或查看拒绝原因。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1. 打开管理端开户申请详情。
+2. 进入审核操作区。
+3. 选择审核拒绝。
+4. 如页面有原因输入，填写“资料不完整”。
+5. 提交后查看状态和原因展示。</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>申请状态变更为审核拒绝；拒绝原因保存并可查看。</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>缺少待审核申请；拒绝原因是否必填需确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>管理端审核通过后才触发提交 BaaS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>可模拟管理端审核通过和 BaaS 提交请求的环境。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1. 准备一条待审核开户申请。
+2. 在 Fidère 管理端审核通过。
+3. 查看 BaaS 提交请求、接口日志或模拟接口调用记录。
+4. 对比未审核通过申请是否无提交记录。</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>未审核通过不提交；审核通过后才触发提交 Interlace/BaaS。</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>提交 BaaS 后管理端展示处理中状态</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>可模拟 BaaS 接收开户资料并返回处理中。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1. 在管理端审核通过开户申请。
+2. 触发 BaaS 提交或模拟提交成功。
+3. 返回管理端申请详情或列表。</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>管理端展示开户处理中或对应中间状态。</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟处理中状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC-050</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>处理中时客户端不可使用美国账户资金功能</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BaaS 开户处理中状态的个人用户。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1. 使用处理中状态用户打开 /admin/product-manual/baas-prototype/opening。
+2. 尝试点击美国账户入金、法币转出或资金互转入口。
+3. 查看按钮状态和提示。</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>客户端不允许使用美国账户入金、转出等资金功能。</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>需模拟开户处理中状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-051</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BaaS 返回成功后管理端状态更新</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>可模拟 BaaS 返回开户成功的申请。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1. 对已提交 BaaS 的申请模拟成功回调。
+2. 打开管理端开户审核详情或列表。
+3. 查看状态。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>管理端状态更新为开户成功。</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>需 BaaS 成功回调或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-052</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BaaS 返回成功后客户端状态更新</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>可模拟 BaaS 返回开户成功的个人用户。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1. 模拟 BaaS 开户成功。
+2. 使用对应用户打开美国账户页面。
+3. 查看开户状态和账户入口。</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>客户端状态更新为开户成功，并展示可用美国账户信息或入口。</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>需 BaaS 成功回调或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC-054</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BaaS 返回失败后客户端和管理端状态更新</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>可模拟 BaaS 返回开户失败的申请。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1. 对已提交 BaaS 的申请模拟失败结果。
+2. 查看 Fidère 管理端申请状态。
+3. 切换到 Fidère 客户端查看用户开户状态。</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>管理端和客户端均展示开户失败状态。</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>需 BaaS 失败回调或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC-057</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Interlace/BaaS 开户结果状态</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>开户失败或拒绝时不得开放资金功能</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>开户失败或拒绝状态的个人用户。</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1. 使用失败或拒绝状态用户打开美国账户页面。
+2. 尝试进入入金、法币转出和资金互转。
+3. 查看入口状态和提示。</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>客户端不得开放美国账户入金、转出等资金功能。</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>需失败/拒绝状态数据或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BaaS 平台</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>美国账户入金场景A</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BaaS 自动生成线下转账入金记录</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BaaS 测试账号；线下转账入金模拟数据。</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1. 在 BaaS 平台或模拟接口准备一笔线下到账记录。
+2. 打开 BaaS 入金记录列表。
+3. 搜索对应用户或金额。</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BaaS 平台出现对应入金记录，金额、币种和用户信息正确。</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟入金记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BaaS 平台</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>美国账户入金场景A</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>运营查看 BaaS 自动入金记录</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>BaaS 测试账号；已生成入金记录。</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1. 运营人工操作登录 BaaS 平台。
+2. 进入入金记录页面。
+3. 打开对应入金记录详情。</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>运营可查看该笔 BaaS 入金记录。</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试账号和入金记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>美国账户入金场景A</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>管理端手动入金入口可进入</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/admin-review。
+2. 进入“法币资产管理”。
+3. 在页面中点击“手动入金”。
+4. 查看抽屉或表单。</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>手动入金入口可进入，页面正常展示。</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>美国账户入金场景A</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>手动入金金额为空校验</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1. 打开手动入金抽屉。
+2. 选择账户类型和客户。
+3. 保持入金金额为空。
+4. 点击“确认入金”。</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示填写金额。</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>美国账户入金场景A</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>手动入金金额为 0 或负数校验</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1. 打开手动入金抽屉。
+2. 在金额中输入 0，再点击确认。
+3. 再输入 -1 或非法格式，点击确认。</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示金额不合法。</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>美国账户入金场景A</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>手动入金后余额或交易记录展示</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>已成功开通美国账户的用户；BaaS 入金记录；Fidère 管理端可手动入金。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1. 在 Fidère 管理端手动入金填写对应用户、美国账户、币种和金额。
+2. 点击“确认入金”。
+3. 切换到 Fidère 客户端查看余额或交易记录。</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>客户端展示对应入金记录或余额变化。</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>待确认余额更新时间和交易记录生成时机；需测试用户和入金记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>已开户成功用户进入美国账户入金页面</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>已最终开户成功的个人用户。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1. 使用开户成功用户打开美国账户页面。
+2. 点击“银行存入”或入金入口。
+3. 查看入金申请页面。</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>入金申请页正常打开。</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>入金金额为空校验</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>已开户成功个人用户。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户入金页面。
+2. 保持金额为空。
+3. 点击提交入金申请。</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示填写金额。</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>入金金额非法值校验</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>已开户成功个人用户。</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户入金页面。
+2. 输入 0、负数或非法格式。
+3. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示金额不合法。</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>客户端提交入金申请后管理端生成待审核记录</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>已开户成功个人用户；可访问 Fidère 管理端。</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1. 客户端提交一笔有效入金申请。
+2. 打开 Fidère 管理端法币资产或入账认领/入金审核相关页面。
+3. 搜索对应用户、金额或时间。</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>管理端生成对应待审核入金申请。</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>缺少开户成功账号或管理端记录联动数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BaaS 平台</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>运营在 BaaS 平台人工录入对应入金数据</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fidère 管理端已有待审核入金申请；BaaS 测试账号。</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1. 打开 Fidère 管理端待审核入金申请并记录用户、账户、金额、币种。
+2. 运营人工操作登录 BaaS 平台。
+3. 根据申请信息创建或录入入金数据。</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BaaS 平台入金数据录入成功。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>管理端审核通过后客户端状态更新</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>待审核入金申请；如需 BaaS 录入，需已完成或模拟完成。</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1. 在 Fidère 管理端打开对应入金申请。
+2. 运营人工操作点击审核通过。
+3. 切换到 Fidère 客户端查看入金状态或交易记录。</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>客户端入金状态更新为审核通过或完成。</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>缺少待审核入金申请；如依赖 BaaS，需模拟完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-091</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>美国账户入金场景B</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>管理端拒绝后客户端展示拒绝状态及原因</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>待审核入金申请。</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1. 在 Fidère 管理端打开对应入金申请。
+2. 运营人工操作选择拒绝并填写原因。
+3. 切换到 Fidère 客户端查看状态。</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>客户端展示拒绝状态及原因。</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>缺少待审核入金申请。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-093</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>已开户成功用户进入美国账户转出页面</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>已最终开户成功且有美国账户的个人用户。</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户页面。
+2. 点击“法币转出”。
+3. 查看转出表单。</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>转出页面正常打开。</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC-099</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>收款人必填校验</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>已开户成功个人用户。</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户法币转出页面。
+2. 保持收款人为空。
+3. 填写金额和用途。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示填写收款人。</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC-100</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>金额必填校验</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>已开户成功个人用户。</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户法币转出页面。
+2. 选择收款人并填写用途。
+3. 保持金额为空。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示填写金额。</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC-101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>转账用途必填校验</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>已开户成功个人用户。</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户法币转出页面。
+2. 选择收款人并填写金额。
+3. 保持转账用途为空。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示填写用途。</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>缺少开户成功测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC-103</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>余额不足拦截</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>美国账户余额不足的个人用户。</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户法币转出页面。
+2. 输入超过可用余额的金额。
+3. 填写收款人和用途。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>系统阻止提交，并提示余额不足。</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>缺少余额不足测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC-104</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>有效转出申请提交</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>美国账户余额充足且有可用收款人的个人用户。</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户法币转出页面。
+2. 选择收款人。
+3. 输入有效金额和用途。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>转出申请提交成功。</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>缺少余额充足账号或收款人数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC-107</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BaaS 平台</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>运营在 BaaS 平台人工创建转出数据</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fidère 管理端已有待审核转出申请；BaaS 测试账号。</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1. 在 Fidère 管理端记录转出申请信息。
+2. 运营人工操作登录 BaaS 平台。
+3. 根据申请信息创建对应转出数据。</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>BaaS 平台转出数据创建成功。</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC-108</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>需人工执行</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BaaS 平台</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BaaS 转出完成并确认实际到账</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>BaaS 平台转出记录；需人工确认到账。</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1. 运营人工操作在 BaaS 平台查看转出处理结果。
+2. 核对银行或平台到账状态。
+3. 标记或记录实际到账确认。</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BaaS 平台显示转出完成或实际到账确认信息。</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>实际到账确认需人工判断，AI 不得盲目判定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC-161</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>进入提现服务费配置页面</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/admin-review。
+2. 点击左侧“提现服务费配置”。
+3. 查看页面标题和配置区域。</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>页面正常展示平台级服务费设置和用户级配置区域。</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC-162</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>平台默认固定金额规则展示</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 查看平台级服务费设置区域。
+3. 定位“固定金额”卡片。</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>页面展示固定金额收费方式、金额和币种。</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC-163</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>平台默认百分比规则展示</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 查看平台级服务费设置区域。
+3. 定位“百分比”卡片。</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>页面展示百分比收费方式及费率。</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC-164</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>平台默认固定金额 + 百分比规则展示</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 查看平台级服务费设置区域。
+3. 定位“固定 + 百分比”卡片。</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>页面展示固定金额、币种及百分比费率。</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC-165</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>当前默认平台规则展示正确</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>使用原型管理端默认数据。</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 查看平台级说明文案。
+3. 检查“未设置用户默认使用平台级固定金额 USD 15.00”或等价信息。</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>页面明确标识当前生效的默认平台规则。</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC-175</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>新增固定金额用户级配置</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>使用可新增配置的测试用户 ID 和邮箱，例如 AI-FEE-001 / ai-fee-fixed@example.com。</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 点击“新增用户配置”。
+3. 填写用户 ID 和邮箱。
+4. 计费方式选择“固定金额”。
+5. 输入 15.00 并保存。</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>保存成功，列表展示该用户的固定金额收费规则。</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC-176</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>新增百分比用户级配置</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>使用可新增配置的测试用户 ID 和邮箱，例如 AI-FEE-002 / ai-fee-percent@example.com。</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 点击“新增用户配置”。
+3. 填写用户 ID 和邮箱。
+4. 计费方式选择“百分比”。
+5. 输入 0.30 并保存。</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>保存成功，列表展示该用户的百分比收费规则。</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TC-177</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>新增固定金额 + 百分比用户级配置</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>使用可新增配置的测试用户 ID 和邮箱，例如 AI-FEE-003 / ai-fee-combo@example.com。</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1. 进入提现服务费配置页面。
+2. 点击“新增用户配置”。
+3. 填写用户 ID 和邮箱。
+4. 计费方式选择“固定手续费 + 百分比”。
+5. 输入 10.00 + 0.20 并保存。</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>保存成功，列表展示该用户的组合收费规则。</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TC-183</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>用户级规则覆盖平台默认规则</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>已配置用户专属规则的测试用户。</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1. 在管理端确认用户存在专属服务费规则。
+2. 修改或查看平台默认规则。
+3. 使用该用户发起法币转出。
+4. 查看转出服务费。</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>该用户仍按自身专属规则计费。</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>缺少已配置用户专属规则且可转出的测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TC-184</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>香港账户法币转出使用平台默认规则计费</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>未配置用户级规则且具备香港账户的用户。</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1. 使用该用户进入香港账户法币转出页面。
+2. 输入有效转出金额。
+3. 查看服务费展示或提交后管理端详情。</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>使用当前平台默认提现服务费规则计费。</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>缺少香港账户测试用户；服务费展示入口待确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TC-185</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>美国账户法币转出使用平台默认规则计费</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>未配置用户级规则且已开通美国账户的用户。</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1. 使用该用户进入美国账户法币转出页面。
+2. 输入有效转出金额。
+3. 查看服务费展示或提交后管理端详情。</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>使用当前平台默认提现服务费规则计费。</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>缺少美国账户测试用户；服务费展示入口待确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TC-199</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>提现服务费配置及法币转出生效</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>美国账户转出管理端审核详情展示服务费</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>已提交美国账户法币转出申请。</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1. 打开 Fidère 管理端出金审批或转出审核详情。
+2. 定位服务费规则和服务费金额。
+3. 核对金额与配置规则。</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>管理端可查看该笔转出的服务费规则和服务费金额。</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>缺少转出申请记录；手续费展示入口待确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TC-116</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>同时具备两类账户的用户可进入互转页面</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>原型默认用户或同时具备香港账户和美国账户的测试用户。</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/opening。
+2. 在香港账户或美国账户卡片点击“资金互转”。
+3. 查看资金互转弹窗或页面。</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>资金互转页面正常打开。</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TC-117</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>未开通成功美国账户时不可互转</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>仅具备香港账户、未成功开通美国账户的用户。</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1. 使用未开通美国账户用户打开账户页面。
+2. 尝试点击资金互转。
+3. 查看入口状态或提示。</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>系统限制发起互转或提示需先开通美国账户。</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>缺少未开通美国账户测试用户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TC-124</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>香港账户转入美国账户成功主流程</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>同时具备香港账户和美国账户且香港账户 USD 余额充足的用户。</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1. 客户端打开资金互转。
+2. 选择香港账户为转出账户、美国账户为转入账户。
+3. 输入有效 USD 金额并提交。
+4. 如需后台审核，使用模拟接口或管理端审核通过。
+5. 查看双方余额和交易记录。</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>互转申请提交成功；审核/模拟完成后香港账户扣减、美国账户增加，交易记录方向正确。</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>需测试数据和可能的后台审核/模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TC-125</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>香港账户转入美国账户余额不足拦截</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>原型默认用户或可输入超额金额的用户。</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1. 打开资金互转。
+2. 选择香港账户 → 美国账户。
+3. 输入超过香港账户可用余额的金额。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>系统拦截提交并提示余额不足。</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TC-135</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>美国账户转入香港账户成功主流程</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>同时具备香港账户和美国账户且美国账户 USD 余额充足的用户。</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1. 客户端打开资金互转。
+2. 选择美国账户为转出账户、香港账户为转入账户。
+3. 输入有效 USD 金额并提交。
+4. 如需后台审核，使用模拟接口或管理端审核通过。
+5. 查看双方余额和交易记录。</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>互转申请提交成功；审核/模拟完成后美国账户扣减、香港账户增加，交易记录方向正确。</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>需测试数据和可能的后台审核/模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TC-136</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>美国账户转入香港账户余额不足拦截</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>原型默认用户或可输入超额金额的用户。</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1. 打开资金互转。
+2. 选择美国账户 → 香港账户。
+3. 输入超过美国账户可用余额的金额。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>系统拦截提交并提示余额不足。</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TC-143</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>需 BaaS 测试环境或模拟接口后执行</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fidère 管理端</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>管理端可查看互转记录且方向不混淆</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>已提交资金互转申请；管理端或模拟接口可生成记录。</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1. 打开管理端 /admin/product-manual/baas-prototype/admin-review。
+2. 进入“法币资产管理” - “资金互转”。
+3. 搜索或打开对应互转记录。
+4. 查看转出账户、转入账户和方向。</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>管理端可查看对应互转记录，方向与账户类型不混淆。</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>需互转申请记录或模拟接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TC-149</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>互转记录不与普通法币转出混淆</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>同时存在互转记录和普通法币转出记录的测试用户。</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1. 完成或准备一条账户互转记录。
+2. 准备一条普通法币转出记录。
+3. 在客户端和管理端交易列表中查看两类记录。</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>账户互转记录不会与普通法币转出记录混淆。</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>缺少互转记录和法币转出记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TC-150</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>需提供测试数据后执行</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>如涉及换汇、手续费或审核则阻塞确认</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>涉及跨币种互转或收费配置的测试场景。</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1. 尝试选择不同币种账户或查看互转费用区域。
+2. 查看页面是否展示汇率、手续费、到账金额和审核状态。
+3. 对照产品确认规则判断。</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>展示结果应符合最终换汇和收费规则；若规则未确认，不判定 PASS。</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BLOCKED-待产品确认：当前原型显示互转仅支持 USD 且不收手续费，需确认是否涉及换汇、手续费、审核和冻结释放规则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TC-152</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>香港账户法币转入/转出回归</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>香港账户仍可进入转入页面</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>原型默认香港账户用户。</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/opening。
+2. 定位香港账户卡片。
+3. 点击银行存入或转入入口。</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>香港账户转入页面正常打开。</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TC-153</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>香港账户法币转入/转出回归</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>香港账户转入主流程正常</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>原型默认香港账户用户。</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1. 进入香港账户转入页面。
+2. 按页面要求查看或填写转入信息。
+3. 点击提交或确认。</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>香港账户转入可正常提交或展示正确提交结果。</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TC-155</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>香港账户法币转入/转出回归</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>香港账户仍可进入法币转出页面</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>原型默认香港账户用户。</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1. 打开账户页面。
+2. 定位香港账户卡片。
+3. 点击“法币转出”。</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>香港账户转出页面正常打开。</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TC-156</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Fidère 客户端</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>香港账户法币转入/转出回归</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>香港账户法币转出主流程正常</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>原型默认香港账户用户。</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1. 进入香港账户法币转出页面。
+2. 选择或填写收款人。
+3. 输入有效金额和用途。
+4. 点击提交。</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>香港账户转出可正常提交。</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TC-160</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>可自动执行</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>多端联动</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>香港账户法币转入/转出回归</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户入口、记录和账户类型不混淆</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>原型默认用户或同时具备香港账户/美国账户的用户。</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1. 在客户端查看香港账户和美国账户入口。
+2. 查看交易记录列表。
+3. 在管理端流水或客户资产中查看账户类型。</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>交易记录和账户类型不会混淆。</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>失败时保留页面截图；记录失败页面、错误提示、实际状态；如可查看控制台或请求，记录异常信息。</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
+++ b/BaaS美国账户开户及资金流程_快速上线测试用例.xlsx
@@ -7,6 +7,7 @@
     <sheet name="主流程及接口覆盖核对版" sheetId="3" r:id="rId3"/>
     <sheet name="待确认项风险汇总" sheetId="4" r:id="rId4"/>
     <sheet name="P0核心场景清单" sheetId="5" r:id="rId5"/>
+    <sheet name="测试专用详细版" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -4366,4 +4367,4140 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I85"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>测试模块</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>用例名称</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>测试步骤</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>预期结果</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>测试数据/备注</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>测试结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DTC-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>个人用户进入美国账户开户页</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>未申请美国账户的个人用户，可访问 BaaS 原型入口。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/opening。
+2. 查看美国账户服务区域。
+3. 点击“创建/继续填写开户申请”或美国账户开户申请入口。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>进入 /admin/product-manual/baas-prototype/account-opening/create；页面展示“BaaS 开户申请”和个人开户资料区域。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>来源：BaasOpeningPrototype、BaasOpeningApplicationPage。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DTC-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>开户页展示 USD 500 开户费提示</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>未申请美国账户的个人用户。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户开户申请页。
+2. 查看页面顶部说明、提交区域和开户费提示。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>页面明确展示开通美国账户将扣除 USD 500 开户费，以及扣费成功后生成开户交易记录。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DTC-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>必填开户资料缺失不可提交</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>开户申请页可编辑。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 清空一个可编辑必填字段或保留必填项为空。
+3. 点击“提交开户申请”。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>页面阻止提交；缺失字段或待补资料区域展示明确错误提示；不进入扣费成功/待审核状态。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DTC-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>必填证明文件缺失不可提交</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>开户资料已填写但至少一个必填文件缺失。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 保持护照/身份证明/地址证明等必填文件缺失。
+3. 点击“提交开户申请”。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>页面阻止提交；提示缺失必填文件；不生成可审核申请。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DTC-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>普通证明文件上传成功</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>准备 PDF/PNG/JPEG 测试文件。</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 在护照或地址证明上传区域选择测试文件。
+3. 等待上传状态变化。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>页面展示文件名或上传成功状态；文件可作为当前有效附件。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DTC-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>普通证明文件替换展示最新文件</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>已有已上传普通证明文件。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1. 在同一文件字段重新选择另一个测试文件。
+2. 完成替换。
+3. 查看文件名和状态。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>页面展示新文件名或更新状态；当前有效文件为新文件。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>文件历史版本规则未完全明确。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DTC-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FATCA 未签署时不可完成提交</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FATCA 或第三方签署状态为未签署。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 保持 FATCA 状态为未签署。
+3. 填写其余资料并点击提交。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>页面提示需完成第三方签署；不应完成开户申请提交。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DTC-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FATCA 签署完成后可继续提交</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>存在可模拟或已完成的 FATCA 签署状态。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1. 点击 FATCA/第三方签署入口。
+2. 完成签署或切换为已签署模拟状态。
+3. 返回开户申请页。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>签署状态展示为已签署；开户申请可继续提交。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>真实第三方签署需测试环境支持。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DTC-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>完整资料提交开户申请成功</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>个人资料完整，必填文件已上传，FATCA 已签署，余额足够扣费。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1. 打开开户申请页。
+2. 确认资料、文件、签署状态齐全。
+3. 点击“提交开户申请”。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>页面显示提交成功；原型提示 USD 500 开户费已扣除并生成开户交易记录；返回开户页后状态进入审核中/待审核。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DTC-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>提交成功后客户端展示待审核</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>已成功提交开户申请。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1. 返回 /admin/product-manual/baas-prototype/opening。
+2. 查看美国账户状态卡。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>客户端展示“审核中/待审核”状态；审核完成前不展示美国账户金额和银行收款信息。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DTC-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>审核拒绝状态展示和重新申请提示</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>美国账户状态为审核拒绝。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1. 在原型顶部状态切换选择“审核拒绝”。
+2. 查看美国账户状态区域。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>页面展示审核拒绝状态和拒绝说明；当前原型提示不提供重新申请入口，需联系运营或客服。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DTC-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>客户端开户流程</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>开户资料修改后重新提交处理</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>已有待修改或可修改申请。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1. 修改开户字段。
+2. 替换普通证明文件。
+3. 如影响签署内容，重新生成/签署第三方文件。
+4. 提交。</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>系统应形成最新待审核版本；管理端可查看最新资料、文件和签署状态。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>当前原型未完整实现修改重提、签署历史版本保留，需产品确认。</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DTC-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>开户费用扣费</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>余额充足时开户费扣费成功</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>个人用户可用余额不低于 USD 500。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1. 完成开户资料填写、文件上传和签署。
+2. 点击“提交开户申请”。
+3. 查看提交成功弹窗或结果区域。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>系统扣除 USD 500 开户费；页面提示扣费成功；申请进入后台审核流程。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DTC-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>开户费用扣费</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>扣费成功生成开户费交易记录</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>开户费扣费成功。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1. 点击“查看开户费交易记录（原型展示）”。
+2. 查看开户费详情。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>交易详情展示“开户费扣款”、个人 BaaS 开户申请、美国账户开户申请、扣费金额 USD 500.00、状态等信息。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DTC-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>开户费用扣费</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>扣费成功后余额减少</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>可查看扣费前后余额。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1. 记录扣费前 USD 可用余额。
+2. 提交开户申请并扣费成功。
+3. 查看余额或交易记录。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>余额减少 USD 500；交易记录金额与开户费一致。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>扣费触发时点和真实余额接口需确认。</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DTC-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>开户费用扣费</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>余额不足时提示并不成功扣费</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>个人用户余额低于 USD 500。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1. 在美国账户页查看开户费余额校验区域。
+2. 尝试提交开户申请并触发扣费。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>页面提示当前可用余额低于 USD 500 开户费；不应产生成功扣费状态。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DTC-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>开户费用扣费</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>重复提交不重复扣费</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>可提交开户申请且余额足够。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1. 快速连续点击“提交开户申请”两次。
+2. 查看交易记录数量和余额变化。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>同一申请只产生一次有效扣费；不得重复扣减 USD 500。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>需要幂等接口或前端防重复提交。</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DTC-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>开户费用扣费</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>开户失败或拒绝后的费用处理</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>开户申请被管理端拒绝或 BaaS/Interlace 拒绝。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1. 将申请置为拒绝/失败。
+2. 查看费用记录、余额和退款状态。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>费用处理应符合最终规则；若退款，应生成退款记录并更新费用状态。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PRD/原型已标注开户失败后 USD 500 是否退回未明确。</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DTC-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>管理端开户审核列表展示申请</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>客户端已提交开户申请。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/admin-review。
+2. 确认左侧为“开户审核”。
+3. 查看申请列表、状态统计和用户信息。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>列表展示对应开户申请；状态、提交时间、用户信息、账户类型可见。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DTC-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>进入开户申请详情查看资料</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>管理端存在待审核申请。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1. 在开户审核列表点击查看详情。
+2. 查看基本信息、个人信息、证件信息、地址信息。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>详情页展示用户提交资料；查看详情态保持只读。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DTC-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>管理端查看普通文件和 FATCA 签署文件</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>申请包含普通证明文件和 FATCA 签署文件。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1. 进入开户申请详情。
+2. 查看附件/文档区域。
+3. 打开普通文件和 FATCA 文件。</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>普通证明文件可查看；FATCA 文件展示已签署/未签署状态。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DTC-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>开始处理时字段卡可编辑</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>待审核申请。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1. 在列表点击“开始处理”。
+2. 查看字段卡片样式。
+3. 编辑一个可修改字段并保存/取消。</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>处理态字段卡展示编辑图标、紫色描边输入框、确认/取消小图标；保存后展示新值，取消后恢复。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DTC-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>审核通过开户申请</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>待审核申请资料无误。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1. 进入处理态。
+2. 在审核决定区域选择审核通过。
+3. 提交审核决定。</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>管理端申请状态变为审核通过；记录审核动作；进入后续 BaaS/Interlace 处理流程。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DTC-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>审核拒绝并展示拒绝原因</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>待审核申请资料不符合要求。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1. 进入处理态。
+2. 选择审核拒绝。
+3. 填写/选择拒绝原因并提交。
+4. 切换客户端查看状态。</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>管理端状态为拒绝；客户端展示拒绝状态和原因。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>当前用户后来要求审核决定删除审核备注，拒绝原因展示方式需确认。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DTC-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>审核未通过不得提交 BaaS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>申请状态为待审核或拒绝。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1. 不执行审核通过。
+2. 查看 BaaS 提交状态或后续处理记录。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>不得触发提交 Interlace/BaaS；不得展示开户处理中/成功。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DTC-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>审核通过后提交或进入 BaaS 处理</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>申请审核通过。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1. 管理端审核通过。
+2. 查看后续状态、外部处理记录或 BaaS 提交提示。</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>按用户确认逻辑应提交 Interlace/BaaS；按原 PRD Phase 1 为 Admin 手动开户并绑定 ID，需明确项目当前实现口径。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>存在 PRD 与用户确认逻辑冲突。</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DTC-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>管理端开户审核</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>提交资料与审核资料一致</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>审核通过后进入 BaaS 提交或人工开户。</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1. 记录审核详情中的姓名、证件、地址、文件。
+2. 查看提交/人工录入资料。
+3. 对比字段。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>提交或人工录入资料与审核通过资料一致，无缺失或错字段。</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DTC-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>开户处理中状态展示</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>申请已提交 BaaS 或等待 Admin 手动开户。</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1. 将美国账户状态置为审核中/处理中。
+2. 查看客户端美国账户页和管理端申请详情。</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>客户端展示审核中/处理中；审核完成前不展示金额和账户收款信息；管理端展示对应中间状态。</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DTC-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>处理中不可使用资金功能</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>美国账户处于审核中/处理中。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1. 在客户端尝试点击银行存入、法币转出、资金互转。</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>入口禁用或不可提交；不得生成入金/转出/互转申请。</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DTC-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>开户成功展示美国账户信息</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户完成并复核通过。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1. 将状态切换为审核通过/Opened。
+2. 查看美国账户页面。</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>客户端展示美国账户服务、银行收款账户/同币种交易/账户信息/账户状态区域和资金功能入口。</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DTC-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>开户成功后开放银行存入入口</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>美国账户开户成功。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1. 在美国账户卡片点击“银行存入”。</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>进入入金/银行存入页面；页面展示美国账户入金相关信息。</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DTC-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>开户成功后开放法币转出入口</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>美国账户开户成功。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1. 在美国账户卡片点击“法币转出”。</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>进入法币转出页面；账户类型可选择/展示美国账户。</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DTC-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>开户成功后开放资金互转入口</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>美国账户开户成功且存在香港账户。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1. 在美国账户或香港账户卡片点击“资金互转”。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>打开资金互转弹窗/页面，可选择香港账户和美国账户方向。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DTC-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BaaS 返回失败或拒绝展示状态与原因</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 返回失败或拒绝。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1. 将状态切换为审核拒绝/失败。
+2. 查看客户端和管理端。</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>客户端和管理端展示失败或拒绝状态；美国账户资金入口不可用。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DTC-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BaaS/Interlace 开户结果</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>客户不可见底层敏感信息</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>开户成功或处理中。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1. 查看客户端美国账户页、交易详情和转出详情。</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>客户端不得展示 Interlace actual balance、raw response、BaaS USDT 地址、OTC cost、Interlace fee、Fidere margin。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PRD 明确客户不可见底层信息。</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DTC-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BaaS 生成线下转账入金记录</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>用户线下向美国账户转账，BaaS 检测到入账。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1. 在 BaaS 测试环境或模拟数据中生成入金记录。
+2. 查看 BaaS 入金记录。</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>BaaS 存在对应入金记录，含用户/账户/金额/币种/时间/参考编号。</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>需要 BaaS 测试环境或模拟接口。</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DTC-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>运营在 Fidère 管理端手动入金</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BaaS 已有可核对入金记录。</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1. 打开管理端 /admin/product-manual/baas-prototype/admin-review。
+2. 进入法币资产管理总览。
+3. 点击“手动入金”。
+4. 选择客户、美国账户、币种、金额并提交。</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>手动入金成功；管理端生成记录；客户端余额或交易记录更新。</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DTC-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>手动入金缺少用户或账户不可提交</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>打开手动入金抽屉。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1. 不选择客户或账户。
+2. 填写金额。
+3. 点击确认入金。</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>系统阻止提交并提示选择用户/账户；不更新余额。</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DTC-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>手动入金金额非法不可提交</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>打开手动入金抽屉。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1. 输入空金额、0、负数或非法格式。
+2. 点击确认入金。</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>系统阻止提交并提示金额不合法；不生成成功记录。</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DTC-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>手动入金后客户端交易记录展示</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>手动入金已完成。</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1. 切换到客户端美国账户页面。
+2. 查看交易记录或余额。</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>客户端展示入金记录或余额增加；状态与管理端一致。</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>余额更新时间和记录生成时机需确认。</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DTC-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fidère 记录与 BaaS 入金记录可核对</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>手动入金记录和 BaaS 入金记录均存在。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1. 在 BaaS 记录中查看 Reference ID/金额/币种。
+2. 在 Fidère 管理端查看手动入金记录。
+3. 对比核对字段。</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>两侧记录可通过用户、账户、金额、币种、Reference ID 或业务编号核对。</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>核对字段需确认。</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DTC-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>已开户成功用户提交入金申请</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>美国账户开户成功。</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1. 客户端进入美国账户页面。
+2. 点击银行存入/入金入口。
+3. 填写金额、币种和必要信息并提交。</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>客户端提交成功，状态为 UNDER_REVIEW/待审核；管理端生成待处理记录。</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DTC-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>入金金额必填和非法值校验</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>美国账户开户成功。</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1. 打开入金申请页。
+2. 金额为空、0、负数或非法格式分别提交。</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>页面阻止提交并提示金额错误；管理端不生成待审核记录。</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DTC-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>管理端收到待审核入金申请</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>客户端已提交入金申请。</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1. 打开管理端。
+2. 进入法币资产管理 - 入账认领/入金相关页。
+3. 搜索对应客户或金额。</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>管理端出现对应待审核/待处理入金申请。</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DTC-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>运营在 BaaS 人工录入入金数据</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>管理端已有待审核入金申请。</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1. 运营记录 Fidère 申请信息。
+2. 登录 BaaS 测试平台。
+3. 人工录入对应入金数据。</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BaaS 平台生成对应入金数据；Fidère 不应自动审核通过。</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>需要 BaaS 测试环境。</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DTC-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>管理端审核通过后余额/记录更新</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BaaS 人工录入完成或已模拟完成。</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1. 回到 Fidère 管理端。
+2. 打开对应入金申请。
+3. 点击审核通过。
+4. 查看客户端余额和交易记录。</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>客户端入金状态更新为完成/通过；余额或交易记录按规则更新。</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DTC-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>管理端审核拒绝后客户端展示原因</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>待审核入金申请。</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1. 管理端拒绝入金申请并填写原因。
+2. 客户端查看入金状态。</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>客户端展示拒绝状态和原因；余额不增加。</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DTC-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>美国账户入金-场景B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fidère 入金申请与 BaaS 数据可核对</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Fidère 入金申请和 BaaS 人工录入记录均存在。</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1. 对比 Fidère 申请编号、金额、币种、用户。
+2. 对比 BaaS Reference ID 或业务编号。</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>两侧数据可核对；核对失败应作为风险记录。</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DTC-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>开户成功用户进入法币转出页</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>美国账户开户成功。</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1. 客户端打开美国账户页面。
+2. 点击“法币转出”。</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>进入法币转出页面；页面标题为“法币转出”；账户类型可见。</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DTC-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>收款人/金额/用途必填校验</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>美国账户开户成功。</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1. 分别缺失收款人、金额、用途提交。</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>页面阻止提交并提示对应必填项；不生成管理端待审核记录。</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DTC-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>余额不足拦截</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>美国账户可用余额低于转出金额及服务费。</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1. 输入超过余额的转出金额。
+2. 提交。</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>页面提示余额不足；不创建转出申请；余额不变。</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DTC-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>有效转出提交生成待审核记录</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>余额充足且收款人有效。</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1. 选择美国账户。
+2. 选择收款人。
+3. 输入金额和用途。
+4. 确认提交。</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>客户端展示待审核/处理中；管理端出金审批生成待审核记录。</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DTC-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>管理端出金审批查看详情</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>已提交转出申请。</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1. 管理端进入法币资产管理 - 出金审批。
+2. 打开对应记录。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>详情展示申请时间、客户、账户类型、转账金额、服务费、实际到账金额、收款人、用途、状态。</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DTC-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>运营在 BaaS 人工创建转出并回填信息</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>管理端待审核转出记录。</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1. 运营在 BaaS 平台创建对应转出。
+2. 回到 Fidère 管理端记录 BaaS Reference ID/回单/执行结果。</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>管理端保存 BaaS 执行信息；状态进入待完成或完成前状态。</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PRD 要求 Manual BaaS Entry、reference 回填、回单上传。</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DTC-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>确认到账后管理端审核通过</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BaaS 转出已完成且确认到账。</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1. 管理端打开转出详情。
+2. 点击审核通过/完成。
+3. 查看客户端状态和交易记录。</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>客户端展示已完成；余额和交易记录正确；管理端状态完成。</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DTC-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>转出拒绝或失败释放余额</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>转出被拒绝或 BaaS 失败。</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1. 管理端拒绝或标记失败。
+2. 查看客户端状态和余额。</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>客户端展示失败/拒绝；冻结金额按规则释放；交易记录状态正确。</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>冻结/释放/手续费退回规则需确认。</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DTC-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>美国账户法币转出</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>客户不可见 BaaS Payee/Payout 底层字段</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>转出详情存在 BaaS 执行信息。</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1. 客户端查看转出详情。
+2. 管理端查看同一详情。</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>客户端只展示客户可见金额、手续费、状态和回单；不展示 BaaS Payee ID、Payout ID、Interlace fee、raw response。</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DTC-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>提现服务费配置</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>进入提现服务费配置页面</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>管理端可访问。</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1. 打开 /admin/product-manual/baas-prototype/admin-review。
+2. 点击左侧“提现服务费配置”。</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>页面展示平台级服务费设置和用户级配置区域。</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DTC-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>提现服务费配置</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>平台默认三类规则展示</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>进入提现服务费配置页。</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1. 查看平台级服务费卡片。</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>页面展示固定金额 USD 15.00、百分比 0.30%、固定 + 百分比 USD 10.00 + 0.20%。</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DTC-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>提现服务费配置</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>新增用户级固定金额规则</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>准备测试用户 ID 和邮箱。</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1. 点击新增用户配置。
+2. 填写用户 ID/邮箱。
+3. 选择固定金额并输入金额。
+4. 保存。</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>用户级配置列表新增记录；计费方式和规则展示正确。</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DTC-061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>提现服务费配置</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>新增用户级百分比和组合规则</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>准备测试用户 ID 和邮箱。</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1. 分别新增百分比规则和固定金额 + 百分比规则。
+2. 保存后查看列表。</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>列表展示百分比规则和组合规则；使用平台默认字段正确。</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DTC-062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>提现服务费配置</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>编辑用户级规则</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>已有用户级服务费配置。</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1. 点击编辑。
+2. 修改计费方式或规则值。
+3. 保存。</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>列表展示更新后的规则；后续转出按新规则或最终生效规则计费。</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>新规则生效时点需确认。</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DTC-063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>提现服务费配置</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>非法服务费配置校验</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>进入新增或编辑弹窗。</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1. 输入负数金额、非法百分比、组合格式错误。
+2. 保存。</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>系统阻止保存并提示输入错误。</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>百分比最大值、精度、舍入规则需确认。</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DTC-064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>香港账户转出使用平台默认服务费</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>用户未配置用户级规则，发起香港账户法币转出。</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1. 客户端进入香港账户法币转出。
+2. 输入金额并查看服务费。
+3. 管理端查看出金详情。</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>服务费按平台默认规则计算；管理端详情展示服务费金额和规则来源。</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DTC-065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>美国账户转出使用平台默认服务费</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>用户未配置用户级规则，发起美国账户法币转出。</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1. 客户端进入美国账户法币转出。
+2. 输入金额并查看服务费。
+3. 管理端查看出金详情。</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>服务费按平台默认规则计算；交易记录包含服务费信息。</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DTC-066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>香港账户转出使用用户级服务费</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>用户已配置用户级固定/百分比/组合规则。</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1. 使用该用户发起香港账户法币转出。
+2. 查看费用计算。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>服务费使用用户级规则，不使用平台默认。</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DTC-067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>美国账户转出使用用户级服务费</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>用户已配置用户级固定/百分比/组合规则。</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1. 使用该用户发起美国账户法币转出。
+2. 查看费用计算。</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>服务费使用用户级规则，不使用平台默认。</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DTC-068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>余额仅够本金但不足服务费时处理</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>用户余额等于转出本金但不足以支付服务费。</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1. 发起香港或美国账户法币转出。
+2. 输入本金金额。
+3. 提交。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>系统按最终内扣/外扣规则拦截或计算；不得产生错误扣款。</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>手续费内扣/外扣规则需确认。</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DTC-069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>转出失败或拒绝后的服务费处理</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>法币转出被拒绝或 BaaS 执行失败。</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1. 管理端拒绝或标记失败。
+2. 查看服务费记录和余额。</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>服务费扣除、退回或不扣除应符合最终规则；交易记录状态正确。</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>失败退费规则需确认。</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DTC-070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>服务费生效验证</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>提交后修改配置的规则快照</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>用户提交转出申请后，运营修改服务费配置。</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1. 记录提交时规则。
+2. 修改平台/用户级规则。
+3. 审核该笔转出。
+4. 查看费用。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>该笔交易应明确使用提交时规则或审核时最新规则，并可追溯。</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>规则快照时点需确认。</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DTC-071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>同时具备双账户用户可进入互转</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>用户拥有香港账户和已成功开通的美国账户。</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1. 打开美国账户/香港账户页面。
+2. 点击“资金互转”。</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>资金互转页面打开；展示转出账户、转入账户、币种、金额等字段。</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DTC-072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>未开通成功美国账户不可互转</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>美国账户未申请、审核中、失败或拒绝。</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1. 尝试打开资金互转或选择美国账户为转入/转出账户。</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>系统限制互转；不生成互转记录。</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DTC-073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>香港账户转入美国账户成功</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>香港账户 USD 余额充足。</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1. 选择香港账户为转出账户，美国账户为转入账户。
+2. 输入 USD 金额。
+3. 确认提交。</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>生成 UNDER_REVIEW 记录；提交后金额冻结并扣减转出账户可用余额；审核通过后美国账户余额增加。</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DTC-074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>美国账户转入香港账户成功</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>美国账户 USD 余额充足。</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1. 选择美国账户为转出账户，香港账户为转入账户。
+2. 输入 USD 金额。
+3. 确认提交。</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>生成 UNDER_REVIEW 记录；审核通过后香港账户余额增加；交易方向为美国账户 → 香港账户。</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DTC-075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>互转余额不足拦截</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>转出账户余额不足。</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1. 选择互转方向。
+2. 输入超过转出账户可用余额的金额。
+3. 提交。</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>系统提示余额不足；不生成有效互转记录；余额不变。</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DTC-076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>互转金额非法校验</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>打开资金互转页面。</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1. 金额为空、0、负数或非法格式提交。</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>系统阻止提交并提示金额错误。</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DTC-077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>管理端资金互转审核</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>客户端已提交互转记录。</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1. 管理端进入法币资产管理 - 资金互转。
+2. 打开对应记录。
+3. 选择审核通过或拒绝。</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>审核通过后转入账户增加余额；拒绝/取消时释放冻结金额；状态展示正确。</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DTC-078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>互转记录不混同入金或法币转出</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>用户存在互转、入金、转出记录。</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1. 客户端查看交易记录。
+2. 管理端查看流水查询和资金互转列表。</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>互转记录展示账户方向和类型，不与普通入金或法币转出混淆。</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DTC-079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户资金互转</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>互转不收提现服务费</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>资金互转页面展示费用说明。</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1. 打开资金互转页面。
+2. 查看费用提示。</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>原型显示资金互转不收取手续费；不默认应用提现服务费。</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>如果后续 PRD 改为收费需更新用例。</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DTC-080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>香港账户回归</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>香港账户法币转入主流程可用</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>用户已具备香港账户。</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1. 客户端打开香港账户区域。
+2. 点击银行存入/转入。
+3. 填写或查看转入信息并提交。</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>香港账户转入流程可正常提交；状态或交易记录展示正常。</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DTC-081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>香港账户回归</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>香港账户法币转出主流程可用</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>用户已具备香港账户。</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1. 点击香港账户“法币转出”。
+2. 填写收款人、金额、用途。
+3. 提交。</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>香港账户转出流程可正常提交；管理端出金审批有对应记录。</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DTC-082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>香港账户回归</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>香港账户与美国账户入口不混淆</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>用户同时具备香港账户和美国账户。</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1. 查看账户页面入口。
+2. 分别点击香港账户和美国账户功能入口。</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>入口、账户类型和页面标题正确，不串到错误账户。</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DTC-083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>香港账户回归</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>香港与美国账户交易记录账户类型正确</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>用户存在两类账户交易记录。</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1. 客户端查看交易记录。
+2. 管理端查看流水查询。</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>交易记录展示账户类型：香港账户/美国账户；金额、方向和状态不混淆。</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DTC-084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>香港账户回归</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>提现服务费在香港账户法币转出中生效</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>香港账户发起法币转出。</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1. 配置平台或用户级服务费。
+2. 发起香港账户转出。
+3. 查看费用和记录。</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>香港账户转出按配置计算服务费；交易记录和管理端详情展示服务费。</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>